--- a/Data/FlightPlan/FPL_08OCT26.xlsx
+++ b/Data/FlightPlan/FPL_08OCT26.xlsx
@@ -503,663 +503,663 @@
     <t>21:00</t>
   </si>
   <si>
+    <t>22:16</t>
+  </si>
+  <si>
+    <t>07:55</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>13:50</t>
+  </si>
+  <si>
+    <t>13:35</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>16:25</t>
+  </si>
+  <si>
+    <t>18:44</t>
+  </si>
+  <si>
+    <t>19:25</t>
+  </si>
+  <si>
+    <t>20:52</t>
+  </si>
+  <si>
+    <t>21:15</t>
+  </si>
+  <si>
+    <t>VN-A543</t>
+  </si>
+  <si>
+    <t>VCA</t>
+  </si>
+  <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>09:08</t>
+  </si>
+  <si>
+    <t>12:02</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>22:05</t>
+  </si>
+  <si>
+    <t>NRT</t>
+  </si>
+  <si>
+    <t>00:30</t>
+  </si>
+  <si>
+    <t>VN-A544</t>
+  </si>
+  <si>
+    <t>06:55</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>08:46</t>
+  </si>
+  <si>
+    <t>BMV</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>UIH</t>
+  </si>
+  <si>
+    <t>15:40</t>
+  </si>
+  <si>
+    <t>17:24</t>
+  </si>
+  <si>
+    <t>19:24</t>
+  </si>
+  <si>
+    <t>PUS</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>07:10</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
+    <t>KHV</t>
+  </si>
+  <si>
+    <t>10:40</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>15:12</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
+    <t>18:08</t>
+  </si>
+  <si>
+    <t>01:50</t>
+  </si>
+  <si>
+    <t>20:05</t>
+  </si>
+  <si>
+    <t>03:54</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
+    <t>12:20</t>
+  </si>
+  <si>
+    <t>01:28</t>
+  </si>
+  <si>
+    <t>VN-A552</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
+    <t>11:10</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>HKG</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>12:25</t>
+  </si>
+  <si>
+    <t>16:23</t>
+  </si>
+  <si>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>17:20</t>
+  </si>
+  <si>
+    <t>19:01</t>
+  </si>
+  <si>
+    <t>21:18</t>
+  </si>
+  <si>
+    <t>02:35</t>
+  </si>
+  <si>
+    <t>VN-A554</t>
+  </si>
+  <si>
+    <t>10:49</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>17:11</t>
+  </si>
+  <si>
+    <t>19:02</t>
+  </si>
+  <si>
+    <t>03:10</t>
+  </si>
+  <si>
+    <t>09:50</t>
+  </si>
+  <si>
+    <t>VN-A575</t>
+  </si>
+  <si>
+    <t>08:10</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t>08:50</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>13:30</t>
+  </si>
+  <si>
+    <t>17:57</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>21:38</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>09:20</t>
+  </si>
+  <si>
+    <t>RMQ</t>
+  </si>
+  <si>
+    <t>18:09</t>
+  </si>
+  <si>
+    <t>19:50</t>
+  </si>
+  <si>
+    <t>20:36</t>
+  </si>
+  <si>
+    <t>01:20</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>VVO</t>
+  </si>
+  <si>
+    <t>12:32</t>
+  </si>
+  <si>
+    <t>00:40</t>
+  </si>
+  <si>
+    <t>BQS</t>
+  </si>
+  <si>
+    <t>01:15</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>14:03</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>00:34</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>10:55</t>
+  </si>
+  <si>
+    <t>14:46</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>11:20</t>
+  </si>
+  <si>
+    <t>12:41</t>
+  </si>
+  <si>
+    <t>16:55</t>
+  </si>
+  <si>
+    <t>13:25</t>
+  </si>
+  <si>
+    <t>17:39</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>19:37</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>07:46</t>
+  </si>
+  <si>
+    <t>10:03</t>
+  </si>
+  <si>
+    <t>10:25</t>
+  </si>
+  <si>
+    <t>12:42</t>
+  </si>
+  <si>
+    <t>15:35</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>17:44</t>
+  </si>
+  <si>
+    <t>18:55</t>
+  </si>
+  <si>
+    <t>22:20</t>
+  </si>
+  <si>
+    <t>01:10</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>DPS</t>
+  </si>
+  <si>
+    <t>08:45</t>
+  </si>
+  <si>
+    <t>16:48</t>
+  </si>
+  <si>
+    <t>17:30</t>
+  </si>
+  <si>
+    <t>20:18</t>
+  </si>
+  <si>
+    <t>MNL</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>12:39</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>14:49</t>
+  </si>
+  <si>
+    <t>17:22</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>19:58</t>
+  </si>
+  <si>
+    <t>20:35</t>
+  </si>
+  <si>
+    <t>22:50</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>06:30</t>
+  </si>
+  <si>
+    <t>07:36</t>
+  </si>
+  <si>
+    <t>09:01</t>
+  </si>
+  <si>
+    <t>11:55</t>
+  </si>
+  <si>
+    <t>13:56</t>
+  </si>
+  <si>
+    <t>17:58</t>
+  </si>
+  <si>
+    <t>20:07</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>22:11</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>09:43</t>
+  </si>
+  <si>
+    <t>16:18</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>19:30</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>DLI</t>
+  </si>
+  <si>
+    <t>09:13</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>11:16</t>
+  </si>
+  <si>
+    <t>13:16</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>18:22</t>
+  </si>
+  <si>
+    <t>18:45</t>
+  </si>
+  <si>
+    <t>20:49</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>16:01</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>18:17</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>21:26</t>
+  </si>
+  <si>
+    <t>23:05</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>15:21</t>
+  </si>
+  <si>
+    <t>18:07</t>
+  </si>
+  <si>
+    <t>20:12</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
+    <t>09:12</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>11:03</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>14:18</t>
+  </si>
+  <si>
+    <t>20:14</t>
+  </si>
+  <si>
+    <t>22:39</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>13:04</t>
+  </si>
+  <si>
+    <t>13:48</t>
+  </si>
+  <si>
+    <t>20:37</t>
+  </si>
+  <si>
+    <t>VN-A643</t>
+  </si>
+  <si>
+    <t>14:23</t>
+  </si>
+  <si>
+    <t>17:53</t>
+  </si>
+  <si>
+    <t>20:28</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>11:17</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>13:22</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>09:31</t>
+  </si>
+  <si>
+    <t>13:07</t>
+  </si>
+  <si>
+    <t>19:11</t>
+  </si>
+  <si>
     <t>21:30</t>
   </si>
   <si>
-    <t>07:55</t>
-  </si>
-  <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>13:50</t>
-  </si>
-  <si>
-    <t>13:35</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>14:30</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>16:25</t>
-  </si>
-  <si>
-    <t>18:44</t>
-  </si>
-  <si>
-    <t>19:25</t>
-  </si>
-  <si>
-    <t>20:52</t>
-  </si>
-  <si>
-    <t>21:15</t>
-  </si>
-  <si>
-    <t>VN-A543</t>
-  </si>
-  <si>
-    <t>VCA</t>
-  </si>
-  <si>
-    <t>06:45</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>09:08</t>
-  </si>
-  <si>
-    <t>12:02</t>
-  </si>
-  <si>
-    <t>14:25</t>
-  </si>
-  <si>
-    <t>19:00</t>
-  </si>
-  <si>
-    <t>20:55</t>
-  </si>
-  <si>
-    <t>22:05</t>
-  </si>
-  <si>
-    <t>NRT</t>
-  </si>
-  <si>
-    <t>00:30</t>
-  </si>
-  <si>
-    <t>VN-A544</t>
-  </si>
-  <si>
-    <t>06:55</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>08:46</t>
-  </si>
-  <si>
-    <t>BMV</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
-    <t>15:40</t>
-  </si>
-  <si>
-    <t>17:24</t>
-  </si>
-  <si>
-    <t>19:24</t>
-  </si>
-  <si>
-    <t>PUS</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>07:10</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>VN-A549</t>
-  </si>
-  <si>
-    <t>KHV</t>
-  </si>
-  <si>
-    <t>10:40</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>15:12</t>
-  </si>
-  <si>
-    <t>14:15</t>
-  </si>
-  <si>
-    <t>18:08</t>
-  </si>
-  <si>
-    <t>01:50</t>
-  </si>
-  <si>
-    <t>20:05</t>
-  </si>
-  <si>
-    <t>03:54</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
-    <t>12:20</t>
-  </si>
-  <si>
-    <t>01:28</t>
-  </si>
-  <si>
-    <t>VN-A552</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>11:10</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>HKG</t>
-  </si>
-  <si>
-    <t>12:10</t>
-  </si>
-  <si>
-    <t>12:25</t>
-  </si>
-  <si>
-    <t>16:23</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>17:20</t>
-  </si>
-  <si>
-    <t>19:01</t>
-  </si>
-  <si>
-    <t>21:18</t>
-  </si>
-  <si>
-    <t>02:35</t>
-  </si>
-  <si>
-    <t>VN-A554</t>
-  </si>
-  <si>
-    <t>10:49</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>17:11</t>
-  </si>
-  <si>
-    <t>19:02</t>
-  </si>
-  <si>
-    <t>03:10</t>
-  </si>
-  <si>
-    <t>09:50</t>
-  </si>
-  <si>
-    <t>VN-A575</t>
-  </si>
-  <si>
-    <t>08:10</t>
-  </si>
-  <si>
-    <t>11:05</t>
-  </si>
-  <si>
-    <t>08:50</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>13:30</t>
-  </si>
-  <si>
-    <t>17:57</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>21:38</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>09:20</t>
-  </si>
-  <si>
-    <t>RMQ</t>
-  </si>
-  <si>
-    <t>18:09</t>
-  </si>
-  <si>
-    <t>19:50</t>
-  </si>
-  <si>
-    <t>20:36</t>
-  </si>
-  <si>
-    <t>01:20</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>VVO</t>
-  </si>
-  <si>
-    <t>12:32</t>
-  </si>
-  <si>
-    <t>00:40</t>
-  </si>
-  <si>
-    <t>BQS</t>
-  </si>
-  <si>
-    <t>01:15</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>14:03</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>00:34</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>10:55</t>
-  </si>
-  <si>
-    <t>14:46</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>10:50</t>
-  </si>
-  <si>
-    <t>11:20</t>
-  </si>
-  <si>
-    <t>12:41</t>
-  </si>
-  <si>
-    <t>16:55</t>
-  </si>
-  <si>
-    <t>13:25</t>
-  </si>
-  <si>
-    <t>17:39</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>19:37</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>07:46</t>
-  </si>
-  <si>
-    <t>10:03</t>
-  </si>
-  <si>
-    <t>10:25</t>
-  </si>
-  <si>
-    <t>12:42</t>
-  </si>
-  <si>
-    <t>15:35</t>
-  </si>
-  <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>16:10</t>
-  </si>
-  <si>
-    <t>17:44</t>
-  </si>
-  <si>
-    <t>18:55</t>
-  </si>
-  <si>
-    <t>22:20</t>
-  </si>
-  <si>
-    <t>22:16</t>
-  </si>
-  <si>
-    <t>01:10</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>DPS</t>
-  </si>
-  <si>
-    <t>08:45</t>
-  </si>
-  <si>
-    <t>16:48</t>
-  </si>
-  <si>
-    <t>17:30</t>
-  </si>
-  <si>
-    <t>20:18</t>
-  </si>
-  <si>
-    <t>MNL</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>12:39</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>14:49</t>
-  </si>
-  <si>
-    <t>17:22</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>19:58</t>
-  </si>
-  <si>
-    <t>20:35</t>
-  </si>
-  <si>
-    <t>22:47</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>06:30</t>
-  </si>
-  <si>
-    <t>07:36</t>
-  </si>
-  <si>
-    <t>09:01</t>
-  </si>
-  <si>
-    <t>11:55</t>
-  </si>
-  <si>
-    <t>13:56</t>
-  </si>
-  <si>
-    <t>17:58</t>
-  </si>
-  <si>
-    <t>20:07</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>VII</t>
-  </si>
-  <si>
-    <t>09:43</t>
-  </si>
-  <si>
-    <t>16:18</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>19:30</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>DLI</t>
-  </si>
-  <si>
-    <t>09:13</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>11:16</t>
-  </si>
-  <si>
-    <t>13:16</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>18:22</t>
-  </si>
-  <si>
-    <t>18:45</t>
-  </si>
-  <si>
-    <t>20:49</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>BKK</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>16:01</t>
-  </si>
-  <si>
-    <t>18:10</t>
-  </si>
-  <si>
-    <t>18:17</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>21:26</t>
-  </si>
-  <si>
-    <t>23:05</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>15:21</t>
-  </si>
-  <si>
-    <t>18:07</t>
-  </si>
-  <si>
-    <t>20:12</t>
-  </si>
-  <si>
-    <t>22:04</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>09:12</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>11:03</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>14:18</t>
-  </si>
-  <si>
-    <t>20:14</t>
-  </si>
-  <si>
-    <t>22:36</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>13:04</t>
-  </si>
-  <si>
-    <t>13:48</t>
-  </si>
-  <si>
-    <t>20:37</t>
-  </si>
-  <si>
-    <t>VN-A643</t>
-  </si>
-  <si>
-    <t>14:23</t>
-  </si>
-  <si>
-    <t>17:53</t>
-  </si>
-  <si>
-    <t>20:28</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>11:17</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>13:22</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
-    <t>06:25</t>
-  </si>
-  <si>
-    <t>09:31</t>
-  </si>
-  <si>
-    <t>13:07</t>
-  </si>
-  <si>
-    <t>19:11</t>
-  </si>
-  <si>
     <t>21:32</t>
   </si>
   <si>
@@ -1787,7 +1787,7 @@
     <t>Total Record(s): 341</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 08, 2026 20:48</t>
+    <t xml:space="preserve">Generated on  Oct 08, 2026 21:10</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -6359,7 +6359,7 @@
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
       <c t="s" r="M134" s="7">
-        <v>296</v>
+        <v>164</v>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1">
@@ -6389,7 +6389,7 @@
         <v>89</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -6422,19 +6422,19 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
+        <v>297</v>
+      </c>
+      <c r="F137" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G137" s="8">
+        <v>28</v>
+      </c>
+      <c t="s" r="H137" s="8">
         <v>298</v>
       </c>
-      <c r="F137" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G137" s="8">
-        <v>28</v>
-      </c>
-      <c t="s" r="H137" s="8">
+      <c t="s" r="I137" s="7">
         <v>299</v>
-      </c>
-      <c t="s" r="I137" s="7">
-        <v>300</v>
       </c>
       <c t="s" r="J137" s="7">
         <v>171</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="L137" s="7"/>
       <c t="s" r="M137" s="7">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="138" ht="14.25" customHeight="1">
@@ -6459,13 +6459,13 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
+        <v>297</v>
+      </c>
+      <c r="F138" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G138" s="8">
         <v>298</v>
-      </c>
-      <c r="F138" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G138" s="8">
-        <v>299</v>
       </c>
       <c t="s" r="H138" s="8">
         <v>28</v>
@@ -6477,11 +6477,11 @@
         <v>98</v>
       </c>
       <c t="s" r="K138" s="7">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L138" s="7"/>
       <c t="s" r="M138" s="7">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="139" ht="14.25" customHeight="1">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -6505,13 +6505,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H139" s="8">
+        <v>303</v>
+      </c>
+      <c t="s" r="I139" s="7">
         <v>304</v>
       </c>
-      <c t="s" r="I139" s="7">
+      <c t="s" r="J139" s="7">
         <v>305</v>
-      </c>
-      <c t="s" r="J139" s="7">
-        <v>306</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -6529,22 +6529,22 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G140" s="8">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c t="s" r="H140" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I140" s="7">
+        <v>306</v>
+      </c>
+      <c t="s" r="J140" s="7">
         <v>307</v>
-      </c>
-      <c t="s" r="J140" s="7">
-        <v>308</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -6577,7 +6577,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -6597,7 +6597,7 @@
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
       <c t="s" r="M142" s="7">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
@@ -6612,7 +6612,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6627,12 +6627,12 @@
         <v>24</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
       <c t="s" r="M143" s="7">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="144" ht="14.25" customHeight="1">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -6667,7 +6667,7 @@
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
       <c t="s" r="M144" s="7">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6697,12 +6697,12 @@
         <v>161</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
       <c t="s" r="M145" s="7">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="146" ht="14.25" customHeight="1">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6729,7 +6729,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c t="s" r="J146" s="7">
         <v>65</v>
@@ -6737,7 +6737,7 @@
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -6767,7 +6767,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6779,7 +6779,7 @@
         <v>196</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c t="s" r="J148" s="7">
         <v>133</v>
@@ -6787,7 +6787,7 @@
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
       <c t="s" r="M148" s="7">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="149" ht="14.25" customHeight="1">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6822,7 +6822,7 @@
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
       <c t="s" r="M149" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="150" ht="15" customHeight="1">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6852,7 +6852,7 @@
         <v>197</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6872,7 +6872,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6892,7 +6892,7 @@
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
       <c t="s" r="M151" s="7">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="152" ht="14.25" customHeight="1">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6942,7 +6942,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6957,12 +6957,12 @@
         <v>175</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
       <c t="s" r="M153" s="7">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="154" ht="14.25" customHeight="1">
@@ -6977,7 +6977,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6997,7 +6997,7 @@
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
       <c t="s" r="M154" s="7">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -7024,14 +7024,16 @@
         <v>28</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
-      <c r="M155" s="7"/>
+      <c t="s" r="M155" s="7">
+        <v>326</v>
+      </c>
     </row>
     <row r="156" ht="14.25" customHeight="1">
       <c r="A156" s="6"/>
@@ -7503,7 +7505,7 @@
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
       <c t="s" r="M170" s="7">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="171" ht="14.25" customHeight="1">
@@ -7713,7 +7715,7 @@
         <v>351</v>
       </c>
       <c t="s" r="K176" s="7">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L176" s="7"/>
       <c t="s" r="M176" s="7">
@@ -7907,7 +7909,7 @@
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>357</v>
+        <v>164</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -7937,7 +7939,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7952,12 +7954,12 @@
         <v>204</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
       <c t="s" r="M184" s="7">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="185" ht="15" customHeight="1">
@@ -7972,7 +7974,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7984,7 +7986,7 @@
         <v>73</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c t="s" r="J185" s="7">
         <v>274</v>
@@ -7994,7 +7996,7 @@
       </c>
       <c r="L185" s="7"/>
       <c t="s" r="M185" s="7">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="186" ht="14.25" customHeight="1">
@@ -8009,7 +8011,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -8021,7 +8023,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c t="s" r="J186" s="7">
         <v>96</v>
@@ -8029,7 +8031,7 @@
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
       <c t="s" r="M186" s="7">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="187" ht="14.25" customHeight="1">
@@ -8044,7 +8046,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -8079,7 +8081,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -8099,7 +8101,7 @@
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
       <c t="s" r="M188" s="7">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
@@ -8114,7 +8116,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -8126,15 +8128,15 @@
         <v>73</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
       <c t="s" r="M189" s="7">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1">
@@ -8164,7 +8166,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -8199,7 +8201,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -8219,7 +8221,7 @@
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
       <c t="s" r="M192" s="7">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="193" ht="14.25" customHeight="1">
@@ -8234,7 +8236,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -8254,7 +8256,7 @@
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
       <c t="s" r="M193" s="7">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="194" ht="14.25" customHeight="1">
@@ -8269,7 +8271,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -8304,7 +8306,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -8319,12 +8321,12 @@
         <v>332</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
       <c t="s" r="M195" s="7">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="196" ht="14.25" customHeight="1">
@@ -8354,7 +8356,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -8376,7 +8378,7 @@
       </c>
       <c r="L197" s="7"/>
       <c t="s" r="M197" s="7">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="198" ht="14.25" customHeight="1">
@@ -8391,7 +8393,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -8411,7 +8413,7 @@
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
       <c t="s" r="M198" s="7">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="199" ht="14.25" customHeight="1">
@@ -8426,7 +8428,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -8446,7 +8448,7 @@
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
       <c t="s" r="M199" s="7">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1">
@@ -8476,7 +8478,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -8496,7 +8498,7 @@
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
       <c t="s" r="M201" s="7">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="202" ht="14.25" customHeight="1">
@@ -8511,7 +8513,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -8523,7 +8525,7 @@
         <v>36</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c t="s" r="J202" s="7">
         <v>153</v>
@@ -8531,7 +8533,7 @@
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -8546,7 +8548,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -8581,7 +8583,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -8616,7 +8618,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8664,7 +8666,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8676,7 +8678,7 @@
         <v>73</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c t="s" r="J207" s="7">
         <v>183</v>
@@ -8684,7 +8686,7 @@
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
       <c t="s" r="M207" s="7">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="208" ht="14.25" customHeight="1">
@@ -8699,7 +8701,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8719,7 +8721,7 @@
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
       <c t="s" r="M208" s="7">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="209" ht="14.25" customHeight="1">
@@ -8734,7 +8736,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8769,7 +8771,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8781,7 +8783,7 @@
         <v>196</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c t="s" r="J210" s="7">
         <v>349</v>
@@ -8789,7 +8791,7 @@
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
       <c t="s" r="M210" s="7">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="211" ht="14.25" customHeight="1">
@@ -8804,7 +8806,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8819,7 +8821,7 @@
         <v>64</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>164</v>
+        <v>382</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -8955,7 +8957,7 @@
         <v>244</v>
       </c>
       <c t="s" r="K216" s="7">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="L216" s="7"/>
       <c t="s" r="M216" s="7">
@@ -9053,7 +9055,7 @@
         <v>36</v>
       </c>
       <c t="s" r="H219" s="8">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c t="s" r="I219" s="7">
         <v>351</v>
@@ -9083,7 +9085,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G220" s="8">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c t="s" r="H220" s="8">
         <v>36</v>
@@ -9217,7 +9219,7 @@
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
       <c t="s" r="M224" s="7">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1">
@@ -9871,7 +9873,7 @@
         <v>73</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c t="s" r="J244" s="7">
         <v>423</v>
@@ -9966,7 +9968,7 @@
       </c>
       <c r="L247" s="7"/>
       <c t="s" r="M247" s="7">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="248" ht="14.25" customHeight="1">
@@ -10115,7 +10117,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c t="s" r="J252" s="7">
         <v>274</v>
@@ -10156,7 +10158,7 @@
         <v>246</v>
       </c>
       <c t="s" r="K253" s="7">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="L253" s="7"/>
       <c t="s" r="M253" s="7">
@@ -10376,7 +10378,7 @@
         <v>20</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
@@ -10408,7 +10410,7 @@
         <v>328</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c t="s" r="J261" s="7">
         <v>208</v>
@@ -10755,7 +10757,7 @@
         <v>36</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c t="s" r="J272" s="7">
         <v>76</v>
@@ -11204,7 +11206,7 @@
         <v>61</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -12023,7 +12025,7 @@
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
       <c t="s" r="M312" s="7">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="313" ht="14.25" customHeight="1">
@@ -12050,7 +12052,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c t="s" r="J313" s="7">
         <v>174</v>
@@ -12241,7 +12243,7 @@
         <v>23</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -12345,7 +12347,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c t="s" r="J322" s="7">
         <v>426</v>
@@ -12355,7 +12357,7 @@
       </c>
       <c r="L322" s="7"/>
       <c t="s" r="M322" s="7">
-        <v>492</v>
+        <v>326</v>
       </c>
     </row>
     <row r="323" ht="14.25" customHeight="1">
@@ -12547,7 +12549,7 @@
         <v>51</v>
       </c>
       <c t="s" r="K328" s="7">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="L328" s="7"/>
       <c t="s" r="M328" s="7">
@@ -12739,7 +12741,7 @@
         <v>61</v>
       </c>
       <c t="s" r="K334" s="7">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L334" s="7"/>
       <c t="s" r="M334" s="7">
@@ -12973,7 +12975,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c t="s" r="J342" s="7">
         <v>271</v>
@@ -13118,7 +13120,7 @@
         <v>129</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -13148,7 +13150,7 @@
         <v>73</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c t="s" r="J347" s="7">
         <v>402</v>
@@ -13204,7 +13206,7 @@
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
       <c t="s" r="M349" s="7">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="350" ht="15" customHeight="1">
@@ -13416,7 +13418,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H356" s="8">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c t="s" r="I356" s="7">
         <v>165</v>
@@ -13448,7 +13450,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G357" s="8">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c t="s" r="H357" s="8">
         <v>28</v>
@@ -13834,7 +13836,7 @@
         <v>460</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c t="s" r="J369" s="7">
         <v>415</v>
@@ -14723,7 +14725,7 @@
         <v>135</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -14838,7 +14840,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c t="s" r="J401" s="7">
         <v>174</v>
@@ -15072,7 +15074,7 @@
         <v>413</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -15187,14 +15189,18 @@
         <v>573</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c t="s" r="J412" s="7">
         <v>111</v>
       </c>
-      <c r="K412" s="7"/>
+      <c t="s" r="K412" s="7">
+        <v>89</v>
+      </c>
       <c r="L412" s="7"/>
-      <c r="M412" s="7"/>
+      <c t="s" r="M412" s="7">
+        <v>210</v>
+      </c>
     </row>
     <row r="413" ht="14.25" customHeight="1">
       <c r="A413" s="6"/>
@@ -15325,10 +15331,10 @@
         <v>169</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>164</v>
+        <v>382</v>
       </c>
       <c t="s" r="K417" s="7">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L417" s="7"/>
       <c t="s" r="M417" s="7">

--- a/Data/FlightPlan/FPL_08OCT26.xlsx
+++ b/Data/FlightPlan/FPL_08OCT26.xlsx
@@ -215,7 +215,7 @@
     <t>20:00</t>
   </si>
   <si>
-    <t>23:56</t>
+    <t>23:50</t>
   </si>
   <si>
     <t>23:35</t>
@@ -281,7 +281,7 @@
     <t>23:00</t>
   </si>
   <si>
-    <t>23:34</t>
+    <t>00:36</t>
   </si>
   <si>
     <t>NGO</t>
@@ -404,6 +404,9 @@
     <t>22:30</t>
   </si>
   <si>
+    <t>23:23</t>
+  </si>
+  <si>
     <t>VN-A534</t>
   </si>
   <si>
@@ -494,6 +497,9 @@
     <t>00:55</t>
   </si>
   <si>
+    <t>00:41</t>
+  </si>
+  <si>
     <t>VN-A536</t>
   </si>
   <si>
@@ -593,6 +599,9 @@
     <t>00:30</t>
   </si>
   <si>
+    <t>07:42</t>
+  </si>
+  <si>
     <t>VN-A544</t>
   </si>
   <si>
@@ -665,7 +674,7 @@
     <t>20:05</t>
   </si>
   <si>
-    <t>03:54</t>
+    <t>03:45</t>
   </si>
   <si>
     <t>VN-A551</t>
@@ -719,6 +728,9 @@
     <t>02:35</t>
   </si>
   <si>
+    <t>03:40</t>
+  </si>
+  <si>
     <t>VN-A554</t>
   </si>
   <si>
@@ -827,6 +839,9 @@
     <t>06:10</t>
   </si>
   <si>
+    <t>06:59</t>
+  </si>
+  <si>
     <t>VN-A629</t>
   </si>
   <si>
@@ -836,6 +851,9 @@
     <t>14:46</t>
   </si>
   <si>
+    <t>06:28</t>
+  </si>
+  <si>
     <t>VN-A630</t>
   </si>
   <si>
@@ -911,6 +929,9 @@
     <t>01:10</t>
   </si>
   <si>
+    <t>02:04</t>
+  </si>
+  <si>
     <t>VN-A633</t>
   </si>
   <si>
@@ -938,6 +959,9 @@
     <t>02:10</t>
   </si>
   <si>
+    <t>02:29</t>
+  </si>
+  <si>
     <t>03:00</t>
   </si>
   <si>
@@ -1076,6 +1100,9 @@
     <t>23:05</t>
   </si>
   <si>
+    <t>00:28</t>
+  </si>
+  <si>
     <t>VN-A640</t>
   </si>
   <si>
@@ -1139,7 +1166,7 @@
     <t>20:28</t>
   </si>
   <si>
-    <t>23:50</t>
+    <t>00:31</t>
   </si>
   <si>
     <t>00:20</t>
@@ -1211,6 +1238,9 @@
     <t>02:40</t>
   </si>
   <si>
+    <t>02:31</t>
+  </si>
+  <si>
     <t>03:35</t>
   </si>
   <si>
@@ -1238,375 +1268,402 @@
     <t>23:20</t>
   </si>
   <si>
+    <t>03:37</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>VDH</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>08:06</t>
+  </si>
+  <si>
+    <t>10:14</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>16:34</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>353D</t>
+  </si>
+  <si>
+    <t>VN-A650</t>
+  </si>
+  <si>
+    <t>08:52</t>
+  </si>
+  <si>
+    <t>10:44</t>
+  </si>
+  <si>
+    <t>12:28</t>
+  </si>
+  <si>
+    <t>16:17</t>
+  </si>
+  <si>
+    <t>19:08</t>
+  </si>
+  <si>
+    <t>21:40</t>
+  </si>
+  <si>
+    <t>00:35</t>
+  </si>
+  <si>
+    <t>02:14</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>12:59</t>
+  </si>
+  <si>
+    <t>21:20</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>22:01</t>
+  </si>
+  <si>
+    <t>07:48</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>10:51</t>
+  </si>
+  <si>
+    <t>14:12</t>
+  </si>
+  <si>
+    <t>16:41</t>
+  </si>
+  <si>
+    <t>18:38</t>
+  </si>
+  <si>
+    <t>PVG</t>
+  </si>
+  <si>
+    <t>01:23</t>
+  </si>
+  <si>
+    <t>02:20</t>
+  </si>
+  <si>
+    <t>04:50</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>06:24</t>
+  </si>
+  <si>
+    <t>12:34</t>
+  </si>
+  <si>
+    <t>16:02</t>
+  </si>
+  <si>
+    <t>18:36</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>12:08</t>
+  </si>
+  <si>
+    <t>15:06</t>
+  </si>
+  <si>
+    <t>18:19</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
+    <t>11:34</t>
+  </si>
+  <si>
+    <t>13:02</t>
+  </si>
+  <si>
+    <t>15:29</t>
+  </si>
+  <si>
+    <t>17:05</t>
+  </si>
+  <si>
+    <t>17:36</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>06:14</t>
+  </si>
+  <si>
+    <t>VN-A663</t>
+  </si>
+  <si>
+    <t>06:46</t>
+  </si>
+  <si>
+    <t>07:15</t>
+  </si>
+  <si>
+    <t>08:32</t>
+  </si>
+  <si>
+    <t>12:49</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>00:19</t>
+  </si>
+  <si>
+    <t>05:09</t>
+  </si>
+  <si>
+    <t>VN-A667</t>
+  </si>
+  <si>
+    <t>02:05</t>
+  </si>
+  <si>
+    <t>VN-A668</t>
+  </si>
+  <si>
+    <t>07:44</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>10:29</t>
+  </si>
+  <si>
+    <t>TXN</t>
+  </si>
+  <si>
+    <t>16:08</t>
+  </si>
+  <si>
+    <t>VN-A669</t>
+  </si>
+  <si>
+    <t>07:57</t>
+  </si>
+  <si>
+    <t>10:31</t>
+  </si>
+  <si>
+    <t>14:38</t>
+  </si>
+  <si>
+    <t>VN-A670</t>
+  </si>
+  <si>
+    <t>13:46</t>
+  </si>
+  <si>
+    <t>16:03</t>
+  </si>
+  <si>
+    <t>18:52</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
+    <t>01:35</t>
+  </si>
+  <si>
+    <t>01:37</t>
+  </si>
+  <si>
+    <t>VN-A671</t>
+  </si>
+  <si>
+    <t>HIJ</t>
+  </si>
+  <si>
+    <t>06:15</t>
+  </si>
+  <si>
+    <t>12:43</t>
+  </si>
+  <si>
+    <t>VN-A672</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>09:51</t>
+  </si>
+  <si>
+    <t>11:31</t>
+  </si>
+  <si>
+    <t>VCL</t>
+  </si>
+  <si>
+    <t>17:01</t>
+  </si>
+  <si>
+    <t>CMB</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>22:27</t>
+  </si>
+  <si>
+    <t>VN-A673</t>
+  </si>
+  <si>
+    <t>10:11</t>
+  </si>
+  <si>
+    <t>11:35</t>
+  </si>
+  <si>
+    <t>11:48</t>
+  </si>
+  <si>
+    <t>14:51</t>
+  </si>
+  <si>
+    <t>20:17</t>
+  </si>
+  <si>
+    <t>22:11</t>
+  </si>
+  <si>
+    <t>VN-A675</t>
+  </si>
+  <si>
+    <t>FSZ</t>
+  </si>
+  <si>
+    <t>14:40</t>
+  </si>
+  <si>
+    <t>17:28</t>
+  </si>
+  <si>
+    <t>19:52</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>00:58</t>
+  </si>
+  <si>
+    <t>VN-A676</t>
+  </si>
+  <si>
+    <t>07:03</t>
+  </si>
+  <si>
+    <t>10:13</t>
+  </si>
+  <si>
+    <t>14:37</t>
+  </si>
+  <si>
+    <t>19:26</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>HAK</t>
+  </si>
+  <si>
+    <t>01:25</t>
+  </si>
+  <si>
+    <t>01:26</t>
+  </si>
+  <si>
+    <t>VN-A677</t>
+  </si>
+  <si>
+    <t>10:09</t>
+  </si>
+  <si>
+    <t>15:54</t>
+  </si>
+  <si>
+    <t>18:04</t>
+  </si>
+  <si>
+    <t>VN-A683</t>
+  </si>
+  <si>
+    <t>08:15</t>
+  </si>
+  <si>
+    <t>08:01</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>14:16</t>
+  </si>
+  <si>
+    <t>01:16</t>
+  </si>
+  <si>
     <t>03:05</t>
   </si>
   <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>VDH</t>
-  </si>
-  <si>
-    <t>06:35</t>
-  </si>
-  <si>
-    <t>08:06</t>
-  </si>
-  <si>
-    <t>10:14</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>14:05</t>
-  </si>
-  <si>
-    <t>16:34</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>353D</t>
-  </si>
-  <si>
-    <t>VN-A650</t>
-  </si>
-  <si>
-    <t>08:52</t>
-  </si>
-  <si>
-    <t>10:44</t>
-  </si>
-  <si>
-    <t>12:28</t>
-  </si>
-  <si>
-    <t>16:17</t>
-  </si>
-  <si>
-    <t>19:08</t>
-  </si>
-  <si>
-    <t>21:40</t>
-  </si>
-  <si>
-    <t>00:35</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>12:59</t>
-  </si>
-  <si>
-    <t>21:20</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>22:01</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>10:51</t>
-  </si>
-  <si>
-    <t>14:12</t>
-  </si>
-  <si>
-    <t>16:41</t>
-  </si>
-  <si>
-    <t>18:38</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>01:23</t>
-  </si>
-  <si>
-    <t>02:20</t>
-  </si>
-  <si>
-    <t>04:50</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
-    <t>06:24</t>
-  </si>
-  <si>
-    <t>12:34</t>
-  </si>
-  <si>
-    <t>16:02</t>
-  </si>
-  <si>
-    <t>18:36</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>10:10</t>
-  </si>
-  <si>
-    <t>12:08</t>
-  </si>
-  <si>
-    <t>15:06</t>
-  </si>
-  <si>
-    <t>18:19</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
-    <t>11:34</t>
-  </si>
-  <si>
-    <t>13:02</t>
-  </si>
-  <si>
-    <t>15:29</t>
-  </si>
-  <si>
-    <t>17:05</t>
-  </si>
-  <si>
-    <t>17:36</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>VN-A663</t>
-  </si>
-  <si>
-    <t>06:46</t>
-  </si>
-  <si>
-    <t>07:15</t>
-  </si>
-  <si>
-    <t>08:32</t>
-  </si>
-  <si>
-    <t>12:49</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>00:19</t>
-  </si>
-  <si>
-    <t>VN-A667</t>
-  </si>
-  <si>
-    <t>02:05</t>
-  </si>
-  <si>
-    <t>VN-A668</t>
-  </si>
-  <si>
-    <t>07:44</t>
-  </si>
-  <si>
-    <t>08:05</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>10:29</t>
-  </si>
-  <si>
-    <t>TXN</t>
-  </si>
-  <si>
-    <t>16:08</t>
-  </si>
-  <si>
-    <t>VN-A669</t>
-  </si>
-  <si>
-    <t>07:57</t>
-  </si>
-  <si>
-    <t>10:31</t>
-  </si>
-  <si>
-    <t>14:38</t>
-  </si>
-  <si>
-    <t>VN-A670</t>
-  </si>
-  <si>
-    <t>13:46</t>
-  </si>
-  <si>
-    <t>16:03</t>
-  </si>
-  <si>
-    <t>18:52</t>
-  </si>
-  <si>
-    <t>23:25</t>
-  </si>
-  <si>
-    <t>01:35</t>
-  </si>
-  <si>
-    <t>VN-A671</t>
-  </si>
-  <si>
-    <t>HIJ</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>12:43</t>
-  </si>
-  <si>
-    <t>VN-A672</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>09:51</t>
-  </si>
-  <si>
-    <t>11:31</t>
-  </si>
-  <si>
-    <t>VCL</t>
-  </si>
-  <si>
-    <t>17:01</t>
-  </si>
-  <si>
-    <t>CMB</t>
-  </si>
-  <si>
-    <t>21:50</t>
-  </si>
-  <si>
-    <t>22:27</t>
-  </si>
-  <si>
-    <t>VN-A673</t>
-  </si>
-  <si>
-    <t>10:11</t>
-  </si>
-  <si>
-    <t>11:35</t>
-  </si>
-  <si>
-    <t>11:48</t>
-  </si>
-  <si>
-    <t>14:51</t>
-  </si>
-  <si>
-    <t>20:17</t>
-  </si>
-  <si>
-    <t>22:11</t>
-  </si>
-  <si>
-    <t>VN-A675</t>
-  </si>
-  <si>
-    <t>FSZ</t>
-  </si>
-  <si>
-    <t>14:40</t>
-  </si>
-  <si>
-    <t>17:28</t>
-  </si>
-  <si>
-    <t>19:52</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>VN-A676</t>
-  </si>
-  <si>
-    <t>07:03</t>
-  </si>
-  <si>
-    <t>10:13</t>
-  </si>
-  <si>
-    <t>14:37</t>
-  </si>
-  <si>
-    <t>19:26</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>HAK</t>
-  </si>
-  <si>
-    <t>01:25</t>
-  </si>
-  <si>
-    <t>VN-A677</t>
-  </si>
-  <si>
-    <t>10:09</t>
-  </si>
-  <si>
-    <t>15:54</t>
-  </si>
-  <si>
-    <t>18:04</t>
-  </si>
-  <si>
-    <t>VN-A683</t>
-  </si>
-  <si>
-    <t>08:15</t>
-  </si>
-  <si>
-    <t>08:01</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>14:16</t>
-  </si>
-  <si>
     <t>VN-A684</t>
   </si>
   <si>
@@ -1658,6 +1715,9 @@
     <t>00:50</t>
   </si>
   <si>
+    <t>01:11</t>
+  </si>
+  <si>
     <t>VN-A689</t>
   </si>
   <si>
@@ -1667,6 +1727,9 @@
     <t>03:55</t>
   </si>
   <si>
+    <t>04:00</t>
+  </si>
+  <si>
     <t>VN-A693</t>
   </si>
   <si>
@@ -1679,7 +1742,7 @@
     <t>23:15</t>
   </si>
   <si>
-    <t>00:08</t>
+    <t>23:30</t>
   </si>
   <si>
     <t>00:15</t>
@@ -1757,6 +1820,9 @@
     <t>05:50</t>
   </si>
   <si>
+    <t>05:47</t>
+  </si>
+  <si>
     <t>VN-A811</t>
   </si>
   <si>
@@ -1778,6 +1844,9 @@
     <t>NQZ</t>
   </si>
   <si>
+    <t>06:53</t>
+  </si>
+  <si>
     <t>VN-A814</t>
   </si>
   <si>
@@ -1802,25 +1871,22 @@
     <t>05:15</t>
   </si>
   <si>
+    <t>09:26</t>
+  </si>
+  <si>
     <t>VN-A817</t>
   </si>
   <si>
     <t>BNE</t>
   </si>
   <si>
-    <t>23:23</t>
-  </si>
-  <si>
-    <t>23:30</t>
-  </si>
-  <si>
-    <t>06:21</t>
+    <t>06:19</t>
   </si>
   <si>
     <t>Total Record(s): 342</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 08, 2026 21:54</t>
+    <t xml:space="preserve">Generated on  Oct 09, 2026 00:50</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3641,7 +3707,9 @@
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
-      <c r="M46" s="7"/>
+      <c t="s" r="M46" s="7">
+        <v>131</v>
+      </c>
     </row>
     <row r="47" ht="14.25" customHeight="1">
       <c r="A47" s="6"/>
@@ -3670,7 +3738,7 @@
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F48" s="7">
         <v>321</v>
@@ -3679,18 +3747,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H48" s="8">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="I48" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="J48" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
       <c t="s" r="M48" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="49" ht="14.25" customHeight="1">
@@ -3705,13 +3773,13 @@
       </c>
       <c r="D49" s="7"/>
       <c t="s" r="E49" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F49" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G49" s="8">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="H49" s="8">
         <v>28</v>
@@ -3720,12 +3788,12 @@
         <v>93</v>
       </c>
       <c t="s" r="J49" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
       <c t="s" r="M49" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
@@ -3740,7 +3808,7 @@
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
@@ -3749,18 +3817,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H50" s="8">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="I50" s="7">
         <v>115</v>
       </c>
       <c t="s" r="J50" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
       <c t="s" r="M50" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="51" ht="14.25" customHeight="1">
@@ -3775,13 +3843,13 @@
       </c>
       <c r="D51" s="7"/>
       <c t="s" r="E51" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F51" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G51" s="8">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="H51" s="8">
         <v>28</v>
@@ -3790,12 +3858,12 @@
         <v>23</v>
       </c>
       <c t="s" r="J51" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
       <c t="s" r="M51" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1">
@@ -3810,7 +3878,7 @@
       </c>
       <c r="D52" s="7"/>
       <c t="s" r="E52" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F52" s="7">
         <v>321</v>
@@ -3819,18 +3887,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H52" s="8">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="I52" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c t="s" r="J52" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
       <c t="s" r="M52" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="53" ht="14.25" customHeight="1">
@@ -3845,13 +3913,13 @@
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G53" s="8">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="H53" s="8">
         <v>28</v>
@@ -3865,7 +3933,7 @@
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
       <c t="s" r="M53" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1">
@@ -3895,7 +3963,7 @@
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
@@ -3907,15 +3975,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I55" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c t="s" r="J55" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
       <c t="s" r="M55" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="56" ht="14.25" customHeight="1">
@@ -3930,7 +3998,7 @@
       </c>
       <c r="D56" s="7"/>
       <c t="s" r="E56" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F56" s="7">
         <v>321</v>
@@ -3942,15 +4010,15 @@
         <v>74</v>
       </c>
       <c t="s" r="I56" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="J56" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
       <c t="s" r="M56" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="57" ht="14.25" customHeight="1">
@@ -3965,7 +4033,7 @@
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
@@ -3977,7 +4045,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I57" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c t="s" r="J57" s="7">
         <v>55</v>
@@ -3985,7 +4053,7 @@
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
       <c t="s" r="M57" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="58" ht="14.25" customHeight="1">
@@ -4000,7 +4068,7 @@
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
@@ -4012,17 +4080,17 @@
         <v>74</v>
       </c>
       <c t="s" r="I58" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c t="s" r="J58" s="7">
         <v>59</v>
       </c>
       <c t="s" r="K58" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L58" s="7"/>
       <c t="s" r="M58" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="59" ht="14.25" customHeight="1">
@@ -4037,7 +4105,7 @@
       </c>
       <c r="D59" s="7"/>
       <c t="s" r="E59" s="7">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F59" s="7">
         <v>321</v>
@@ -4049,14 +4117,16 @@
         <v>28</v>
       </c>
       <c t="s" r="I59" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c t="s" r="J59" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
-      <c r="M59" s="7"/>
+      <c t="s" r="M59" s="7">
+        <v>162</v>
+      </c>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" s="6"/>
@@ -4085,7 +4155,7 @@
       </c>
       <c r="D61" s="7"/>
       <c t="s" r="E61" s="7">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F61" s="7">
         <v>321</v>
@@ -4097,7 +4167,7 @@
         <v>36</v>
       </c>
       <c t="s" r="I61" s="7">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c t="s" r="J61" s="7">
         <v>30</v>
@@ -4107,7 +4177,7 @@
       </c>
       <c r="L61" s="7"/>
       <c t="s" r="M61" s="7">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="62" ht="14.25" customHeight="1">
@@ -4122,7 +4192,7 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
@@ -4137,14 +4207,14 @@
         <v>102</v>
       </c>
       <c t="s" r="J62" s="7">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c t="s" r="K62" s="7">
         <v>86</v>
       </c>
       <c r="L62" s="7"/>
       <c t="s" r="M62" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="63" ht="14.25" customHeight="1">
@@ -4159,7 +4229,7 @@
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
@@ -4174,7 +4244,7 @@
         <v>92</v>
       </c>
       <c t="s" r="J63" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
@@ -4207,7 +4277,7 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
@@ -4216,20 +4286,20 @@
         <v>28</v>
       </c>
       <c t="s" r="H65" s="8">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c t="s" r="I65" s="7">
         <v>113</v>
       </c>
       <c t="s" r="J65" s="7">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c t="s" r="K65" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="L65" s="7"/>
       <c t="s" r="M65" s="7">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="66" ht="14.25" customHeight="1">
@@ -4244,29 +4314,29 @@
       </c>
       <c r="D66" s="7"/>
       <c t="s" r="E66" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F66" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G66" s="8">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c t="s" r="H66" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I66" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c t="s" r="J66" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c t="s" r="K66" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="L66" s="7"/>
       <c t="s" r="M66" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="67" ht="14.25" customHeight="1">
@@ -4281,7 +4351,7 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
@@ -4293,17 +4363,17 @@
         <v>74</v>
       </c>
       <c t="s" r="I67" s="7">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c t="s" r="J67" s="7">
         <v>47</v>
       </c>
       <c t="s" r="K67" s="7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L67" s="7"/>
       <c t="s" r="M67" s="7">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="68" ht="14.25" customHeight="1">
@@ -4318,7 +4388,7 @@
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
@@ -4330,7 +4400,7 @@
         <v>36</v>
       </c>
       <c t="s" r="I68" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c t="s" r="J68" s="7">
         <v>88</v>
@@ -4338,7 +4408,7 @@
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
       <c t="s" r="M68" s="7">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
@@ -4353,7 +4423,7 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
@@ -4365,7 +4435,7 @@
         <v>74</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c t="s" r="J69" s="7">
         <v>66</v>
@@ -4373,7 +4443,7 @@
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
       <c t="s" r="M69" s="7">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
@@ -4403,7 +4473,7 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -4412,18 +4482,18 @@
         <v>74</v>
       </c>
       <c t="s" r="H71" s="8">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
       <c t="s" r="M71" s="7">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1">
@@ -4438,13 +4508,13 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G72" s="8">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c t="s" r="H72" s="8">
         <v>74</v>
@@ -4458,7 +4528,7 @@
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
       <c t="s" r="M72" s="7">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="73" ht="14.25" customHeight="1">
@@ -4473,7 +4543,7 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
@@ -4485,7 +4555,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I73" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c t="s" r="J73" s="7">
         <v>124</v>
@@ -4508,7 +4578,7 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
@@ -4520,15 +4590,15 @@
         <v>74</v>
       </c>
       <c t="s" r="I74" s="7">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
       <c t="s" r="M74" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
@@ -4543,7 +4613,7 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
@@ -4552,17 +4622,19 @@
         <v>74</v>
       </c>
       <c t="s" r="H75" s="8">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c t="s" r="I75" s="7">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c t="s" r="J75" s="7">
         <v>93</v>
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
-      <c r="M75" s="7"/>
+      <c t="s" r="M75" s="7">
+        <v>196</v>
+      </c>
     </row>
     <row r="76" ht="14.25" customHeight="1">
       <c r="A76" s="6"/>
@@ -4591,7 +4663,7 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
@@ -4603,15 +4675,15 @@
         <v>74</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
       <c t="s" r="M77" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="78" ht="14.25" customHeight="1">
@@ -4626,7 +4698,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -4635,10 +4707,10 @@
         <v>74</v>
       </c>
       <c t="s" r="H78" s="8">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c t="s" r="J78" s="7">
         <v>41</v>
@@ -4661,27 +4733,27 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G79" s="8">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="H79" s="8">
         <v>74</v>
       </c>
       <c t="s" r="I79" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
       <c t="s" r="M79" s="7">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
@@ -4696,7 +4768,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -4705,10 +4777,10 @@
         <v>74</v>
       </c>
       <c t="s" r="H80" s="8">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c t="s" r="J80" s="7">
         <v>59</v>
@@ -4716,7 +4788,7 @@
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
       <c t="s" r="M80" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
@@ -4731,13 +4803,13 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G81" s="8">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="H81" s="8">
         <v>74</v>
@@ -4746,12 +4818,12 @@
         <v>61</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
       <c t="s" r="M81" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
@@ -4766,7 +4838,7 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -4775,13 +4847,13 @@
         <v>74</v>
       </c>
       <c t="s" r="H82" s="8">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
@@ -4810,33 +4882,33 @@
         <v>3524</v>
       </c>
       <c t="s" r="C84" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G84" s="8">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c t="s" r="H84" s="8">
         <v>74</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c t="s" r="K84" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="L84" s="7"/>
       <c t="s" r="M84" s="7">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
@@ -4847,11 +4919,11 @@
         <v>3524</v>
       </c>
       <c t="s" r="C85" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
@@ -4863,7 +4935,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c t="s" r="J85" s="7">
         <v>58</v>
@@ -4873,7 +4945,7 @@
       </c>
       <c r="L85" s="7"/>
       <c t="s" r="M85" s="7">
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
@@ -4888,7 +4960,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4903,14 +4975,14 @@
         <v>125</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c t="s" r="K86" s="7">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="L86" s="7"/>
       <c t="s" r="M86" s="7">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="87" ht="14.25" customHeight="1">
@@ -4940,7 +5012,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4952,17 +5024,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c t="s" r="K88" s="7">
         <v>118</v>
       </c>
       <c r="L88" s="7"/>
       <c t="s" r="M88" s="7">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="89" ht="14.25" customHeight="1">
@@ -4977,7 +5049,7 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4989,15 +5061,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
       <c t="s" r="M89" s="7">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1">
@@ -5027,27 +5099,27 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G91" s="8">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c t="s" r="H91" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
       <c t="s" r="M91" s="7">
-        <v>225</v>
+        <v>228</v>
       </c>
     </row>
     <row r="92" ht="14.25" customHeight="1">
@@ -5062,7 +5134,7 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -5071,20 +5143,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H92" s="8">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c t="s" r="J92" s="7">
         <v>121</v>
       </c>
       <c t="s" r="K92" s="7">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="L92" s="7"/>
       <c t="s" r="M92" s="7">
-        <v>229</v>
+        <v>232</v>
       </c>
     </row>
     <row r="93" ht="14.25" customHeight="1">
@@ -5099,29 +5171,29 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G93" s="8">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c t="s" r="H93" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c t="s" r="K93" s="7">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="L93" s="7"/>
       <c t="s" r="M93" s="7">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="94" ht="14.25" customHeight="1">
@@ -5136,7 +5208,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -5158,7 +5230,7 @@
       </c>
       <c r="L94" s="7"/>
       <c t="s" r="M94" s="7">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
@@ -5173,7 +5245,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -5185,14 +5257,18 @@
         <v>16</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>151</v>
-      </c>
-      <c r="K95" s="7"/>
+        <v>152</v>
+      </c>
+      <c t="s" r="K95" s="7">
+        <v>239</v>
+      </c>
       <c r="L95" s="7"/>
-      <c r="M95" s="7"/>
+      <c t="s" r="M95" s="7">
+        <v>115</v>
+      </c>
     </row>
     <row r="96" ht="14.25" customHeight="1">
       <c r="A96" s="6"/>
@@ -5217,11 +5293,11 @@
         <v>7621</v>
       </c>
       <c t="s" r="C97" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -5241,7 +5317,7 @@
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
       <c t="s" r="M97" s="7">
-        <v>237</v>
+        <v>241</v>
       </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
@@ -5256,7 +5332,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -5271,12 +5347,12 @@
         <v>97</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
       <c t="s" r="M98" s="7">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="99" ht="14.25" customHeight="1">
@@ -5291,7 +5367,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -5306,12 +5382,12 @@
         <v>124</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
       <c t="s" r="M99" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1">
@@ -5326,7 +5402,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -5335,13 +5411,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H100" s="8">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -5374,29 +5450,29 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G102" s="8">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c t="s" r="H102" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c t="s" r="K102" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="L102" s="7"/>
       <c t="s" r="M102" s="7">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="103" ht="14.25" customHeight="1">
@@ -5411,7 +5487,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -5423,7 +5499,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c t="s" r="J103" s="7">
         <v>124</v>
@@ -5431,7 +5507,7 @@
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
       <c t="s" r="M103" s="7">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="104" ht="14.25" customHeight="1">
@@ -5446,7 +5522,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -5458,15 +5534,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
       <c t="s" r="M104" s="7">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
@@ -5496,7 +5572,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -5508,10 +5584,10 @@
         <v>74</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -5531,7 +5607,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -5540,18 +5616,18 @@
         <v>74</v>
       </c>
       <c t="s" r="H107" s="8">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
       <c t="s" r="M107" s="7">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
@@ -5566,13 +5642,13 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G108" s="8">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c t="s" r="H108" s="8">
         <v>74</v>
@@ -5581,14 +5657,14 @@
         <v>124</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c t="s" r="K108" s="7">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="L108" s="7"/>
       <c t="s" r="M108" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
     </row>
     <row r="109" ht="14.25" customHeight="1">
@@ -5603,7 +5679,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -5615,7 +5691,7 @@
         <v>32</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c t="s" r="J109" s="7">
         <v>110</v>
@@ -5651,27 +5727,27 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G111" s="8">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c t="s" r="H111" s="8">
         <v>74</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
       <c t="s" r="M111" s="7">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="112" ht="14.25" customHeight="1">
@@ -5686,7 +5762,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5698,7 +5774,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="J112" s="7">
         <v>120</v>
@@ -5717,11 +5793,11 @@
         <v>7614</v>
       </c>
       <c t="s" r="C113" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5736,11 +5812,13 @@
         <v>103</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
-      <c r="M113" s="7"/>
+      <c t="s" r="M113" s="7">
+        <v>161</v>
+      </c>
     </row>
     <row r="114" ht="14.25" customHeight="1">
       <c t="s" r="A114" s="6">
@@ -5750,11 +5828,11 @@
         <v>7614</v>
       </c>
       <c t="s" r="C114" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5763,10 +5841,10 @@
         <v>74</v>
       </c>
       <c t="s" r="H114" s="8">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c t="s" r="J114" s="7">
         <v>22</v>
@@ -5802,19 +5880,19 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G116" s="8">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c t="s" r="H116" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c t="s" r="J116" s="7">
         <v>78</v>
@@ -5822,7 +5900,7 @@
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
       <c t="s" r="M116" s="7">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
@@ -5837,7 +5915,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5846,10 +5924,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H117" s="8">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c t="s" r="J117" s="7">
         <v>33</v>
@@ -5857,7 +5935,7 @@
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
       <c t="s" r="M117" s="7">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
@@ -5872,26 +5950,28 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G118" s="8">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c t="s" r="H118" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
-      <c r="M118" s="7"/>
+      <c t="s" r="M118" s="7">
+        <v>276</v>
+      </c>
     </row>
     <row r="119" ht="14.25" customHeight="1">
       <c r="A119" s="6"/>
@@ -5920,29 +6000,29 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G120" s="8">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c t="s" r="H120" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c t="s" r="K120" s="7">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="L120" s="7"/>
       <c t="s" r="M120" s="7">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="121" ht="14.25" customHeight="1">
@@ -5957,7 +6037,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5976,7 +6056,9 @@
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
-      <c r="M121" s="7"/>
+      <c t="s" r="M121" s="7">
+        <v>280</v>
+      </c>
     </row>
     <row r="122" ht="14.25" customHeight="1">
       <c r="A122" s="6"/>
@@ -6005,7 +6087,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -6014,18 +6096,18 @@
         <v>36</v>
       </c>
       <c t="s" r="H123" s="8">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="I123" s="7">
         <v>113</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
       <c t="s" r="M123" s="7">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="124" ht="14.25" customHeight="1">
@@ -6040,27 +6122,27 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G124" s="8">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="H124" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
       <c t="s" r="M124" s="7">
-        <v>278</v>
+        <v>284</v>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1">
@@ -6075,7 +6157,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -6087,17 +6169,17 @@
         <v>95</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c t="s" r="K125" s="7">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="L125" s="7"/>
       <c t="s" r="M125" s="7">
-        <v>281</v>
+        <v>287</v>
       </c>
     </row>
     <row r="126" ht="14.25" customHeight="1">
@@ -6112,7 +6194,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -6124,17 +6206,17 @@
         <v>28</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c t="s" r="K126" s="7">
         <v>125</v>
       </c>
       <c r="L126" s="7"/>
       <c t="s" r="M126" s="7">
-        <v>283</v>
+        <v>289</v>
       </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
@@ -6164,7 +6246,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -6173,18 +6255,18 @@
         <v>74</v>
       </c>
       <c t="s" r="H128" s="8">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
       <c t="s" r="M128" s="7">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="129" ht="14.25" customHeight="1">
@@ -6199,27 +6281,27 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G129" s="8">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="H129" s="8">
         <v>74</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
       <c t="s" r="M129" s="7">
-        <v>288</v>
+        <v>294</v>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1">
@@ -6234,7 +6316,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -6243,18 +6325,18 @@
         <v>74</v>
       </c>
       <c t="s" r="H130" s="8">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
       <c t="s" r="M130" s="7">
-        <v>290</v>
+        <v>296</v>
       </c>
     </row>
     <row r="131" ht="14.25" customHeight="1">
@@ -6269,13 +6351,13 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G131" s="8">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c t="s" r="H131" s="8">
         <v>74</v>
@@ -6284,12 +6366,12 @@
         <v>24</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
       <c t="s" r="M131" s="7">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="132" ht="14.25" customHeight="1">
@@ -6304,7 +6386,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -6313,20 +6395,20 @@
         <v>74</v>
       </c>
       <c t="s" r="H132" s="8">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c t="s" r="I132" s="7">
         <v>121</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c t="s" r="K132" s="7">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="L132" s="7"/>
       <c t="s" r="M132" s="7">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="133" ht="14.25" customHeight="1">
@@ -6341,13 +6423,13 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G133" s="8">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c t="s" r="H133" s="8">
         <v>74</v>
@@ -6356,14 +6438,14 @@
         <v>46</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c t="s" r="K133" s="7">
         <v>47</v>
       </c>
       <c r="L133" s="7"/>
       <c t="s" r="M133" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="134" ht="14.25" customHeight="1">
@@ -6378,7 +6460,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -6393,12 +6475,12 @@
         <v>86</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
       <c t="s" r="M134" s="7">
-        <v>298</v>
+        <v>304</v>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1">
@@ -6413,7 +6495,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -6428,11 +6510,13 @@
         <v>89</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
-      <c r="M135" s="7"/>
+      <c t="s" r="M135" s="7">
+        <v>306</v>
+      </c>
     </row>
     <row r="136" ht="14.25" customHeight="1">
       <c r="A136" s="6"/>
@@ -6461,7 +6545,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -6470,20 +6554,20 @@
         <v>28</v>
       </c>
       <c t="s" r="H137" s="8">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c t="s" r="K137" s="7">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L137" s="7"/>
       <c t="s" r="M137" s="7">
-        <v>303</v>
+        <v>310</v>
       </c>
     </row>
     <row r="138" ht="14.25" customHeight="1">
@@ -6498,13 +6582,13 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G138" s="8">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c t="s" r="H138" s="8">
         <v>28</v>
@@ -6516,11 +6600,11 @@
         <v>99</v>
       </c>
       <c t="s" r="K138" s="7">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="L138" s="7"/>
       <c t="s" r="M138" s="7">
-        <v>305</v>
+        <v>312</v>
       </c>
     </row>
     <row r="139" ht="14.25" customHeight="1">
@@ -6535,7 +6619,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -6544,17 +6628,19 @@
         <v>28</v>
       </c>
       <c t="s" r="H139" s="8">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
-      <c r="M139" s="7"/>
+      <c t="s" r="M139" s="7">
+        <v>316</v>
+      </c>
     </row>
     <row r="140" ht="15" customHeight="1">
       <c t="s" r="A140" s="6">
@@ -6568,22 +6654,22 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G140" s="8">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c t="s" r="H140" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -6616,27 +6702,27 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G142" s="8">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="H142" s="8">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
       <c t="s" r="M142" s="7">
-        <v>312</v>
+        <v>320</v>
       </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
@@ -6651,27 +6737,27 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G143" s="8">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="H143" s="8">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="I143" s="7">
         <v>24</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
       <c t="s" r="M143" s="7">
-        <v>314</v>
+        <v>322</v>
       </c>
     </row>
     <row r="144" ht="14.25" customHeight="1">
@@ -6686,27 +6772,27 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G144" s="8">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="H144" s="8">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
       <c t="s" r="M144" s="7">
-        <v>315</v>
+        <v>323</v>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1">
@@ -6721,27 +6807,27 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G145" s="8">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c t="s" r="H145" s="8">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
       <c t="s" r="M145" s="7">
-        <v>317</v>
+        <v>325</v>
       </c>
     </row>
     <row r="146" ht="14.25" customHeight="1">
@@ -6756,19 +6842,19 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G146" s="8">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="H146" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c t="s" r="J146" s="7">
         <v>66</v>
@@ -6776,7 +6862,7 @@
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
-        <v>319</v>
+        <v>327</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -6806,7 +6892,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6815,18 +6901,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H148" s="8">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
       <c t="s" r="M148" s="7">
-        <v>322</v>
+        <v>330</v>
       </c>
     </row>
     <row r="149" ht="14.25" customHeight="1">
@@ -6841,13 +6927,13 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G149" s="8">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="H149" s="8">
         <v>28</v>
@@ -6861,7 +6947,7 @@
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
       <c t="s" r="M149" s="7">
-        <v>323</v>
+        <v>331</v>
       </c>
     </row>
     <row r="150" ht="15" customHeight="1">
@@ -6876,7 +6962,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6885,18 +6971,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H150" s="8">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
       <c t="s" r="M150" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="151" ht="14.25" customHeight="1">
@@ -6911,27 +6997,27 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G151" s="8">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c t="s" r="H151" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
       <c t="s" r="M151" s="7">
-        <v>325</v>
+        <v>333</v>
       </c>
     </row>
     <row r="152" ht="14.25" customHeight="1">
@@ -6946,7 +7032,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6981,7 +7067,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6993,15 +7079,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
       <c t="s" r="M153" s="7">
-        <v>326</v>
+        <v>334</v>
       </c>
     </row>
     <row r="154" ht="14.25" customHeight="1">
@@ -7016,7 +7102,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -7028,15 +7114,15 @@
         <v>36</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
       <c t="s" r="M154" s="7">
-        <v>327</v>
+        <v>335</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
@@ -7051,7 +7137,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -7063,15 +7149,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
       <c t="s" r="M155" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="156" ht="14.25" customHeight="1">
@@ -7101,7 +7187,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -7110,18 +7196,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H157" s="8">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
       <c t="s" r="M157" s="7">
-        <v>331</v>
+        <v>339</v>
       </c>
     </row>
     <row r="158" ht="14.25" customHeight="1">
@@ -7136,13 +7222,13 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G158" s="8">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c t="s" r="H158" s="8">
         <v>28</v>
@@ -7151,12 +7237,12 @@
         <v>38</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
       <c t="s" r="M158" s="7">
-        <v>227</v>
+        <v>230</v>
       </c>
     </row>
     <row r="159" ht="14.25" customHeight="1">
@@ -7171,7 +7257,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -7186,12 +7272,12 @@
         <v>25</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
       <c t="s" r="M159" s="7">
-        <v>332</v>
+        <v>340</v>
       </c>
     </row>
     <row r="160" ht="15" customHeight="1">
@@ -7206,7 +7292,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -7218,15 +7304,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
       <c t="s" r="M160" s="7">
-        <v>334</v>
+        <v>342</v>
       </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
@@ -7256,7 +7342,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -7265,18 +7351,18 @@
         <v>74</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
       <c t="s" r="M162" s="7">
-        <v>337</v>
+        <v>345</v>
       </c>
     </row>
     <row r="163" ht="14.25" customHeight="1">
@@ -7291,29 +7377,29 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c t="s" r="H163" s="8">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c t="s" r="K163" s="7">
         <v>96</v>
       </c>
       <c r="L163" s="7"/>
       <c t="s" r="M163" s="7">
-        <v>339</v>
+        <v>347</v>
       </c>
     </row>
     <row r="164" ht="14.25" customHeight="1">
@@ -7328,29 +7414,29 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G164" s="8">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c t="s" r="H164" s="8">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c t="s" r="J164" s="7">
         <v>24</v>
       </c>
       <c t="s" r="K164" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L164" s="7"/>
       <c t="s" r="M164" s="7">
-        <v>340</v>
+        <v>348</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1">
@@ -7365,29 +7451,29 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G165" s="8">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c t="s" r="H165" s="8">
         <v>74</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c t="s" r="K165" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L165" s="7"/>
       <c t="s" r="M165" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
@@ -7402,7 +7488,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -7411,20 +7497,20 @@
         <v>74</v>
       </c>
       <c t="s" r="H166" s="8">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c t="s" r="K166" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L166" s="7"/>
       <c t="s" r="M166" s="7">
-        <v>342</v>
+        <v>350</v>
       </c>
     </row>
     <row r="167" ht="14.25" customHeight="1">
@@ -7439,29 +7525,29 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G167" s="8">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c t="s" r="H167" s="8">
         <v>74</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c t="s" r="J167" s="7">
         <v>86</v>
       </c>
       <c t="s" r="K167" s="7">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="L167" s="7"/>
       <c t="s" r="M167" s="7">
-        <v>344</v>
+        <v>352</v>
       </c>
     </row>
     <row r="168" ht="14.25" customHeight="1">
@@ -7476,7 +7562,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -7488,7 +7574,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c t="s" r="J168" s="7">
         <v>69</v>
@@ -7496,7 +7582,7 @@
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
       <c t="s" r="M168" s="7">
-        <v>345</v>
+        <v>353</v>
       </c>
     </row>
     <row r="169" ht="14.25" customHeight="1">
@@ -7526,7 +7612,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -7538,15 +7624,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
       <c t="s" r="M170" s="7">
-        <v>322</v>
+        <v>330</v>
       </c>
     </row>
     <row r="171" ht="14.25" customHeight="1">
@@ -7561,7 +7647,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -7570,18 +7656,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H171" s="8">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c t="s" r="I171" s="7">
         <v>22</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
       <c t="s" r="M171" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="172" ht="14.25" customHeight="1">
@@ -7596,19 +7682,19 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G172" s="8">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c t="s" r="H172" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c t="s" r="J172" s="7">
         <v>77</v>
@@ -7631,7 +7717,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -7640,7 +7726,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c t="s" r="I173" s="7">
         <v>79</v>
@@ -7651,7 +7737,7 @@
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
       <c t="s" r="M173" s="7">
-        <v>349</v>
+        <v>357</v>
       </c>
     </row>
     <row r="174" ht="14.25" customHeight="1">
@@ -7666,27 +7752,27 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G174" s="8">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c t="s" r="H174" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
       <c t="s" r="M174" s="7">
-        <v>351</v>
+        <v>359</v>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1">
@@ -7701,7 +7787,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -7713,17 +7799,17 @@
         <v>74</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c t="s" r="K175" s="7">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="L175" s="7"/>
       <c t="s" r="M175" s="7">
-        <v>353</v>
+        <v>361</v>
       </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
@@ -7738,7 +7824,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7750,17 +7836,17 @@
         <v>28</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c t="s" r="K176" s="7">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="L176" s="7"/>
       <c t="s" r="M176" s="7">
-        <v>83</v>
+        <v>363</v>
       </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
@@ -7790,22 +7876,22 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G178" s="8">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c t="s" r="H178" s="8">
         <v>74</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -7825,7 +7911,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7845,7 +7931,7 @@
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
       <c t="s" r="M179" s="7">
-        <v>357</v>
+        <v>366</v>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1">
@@ -7860,7 +7946,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7872,7 +7958,7 @@
         <v>74</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c t="s" r="J180" s="7">
         <v>61</v>
@@ -7880,7 +7966,7 @@
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
       <c t="s" r="M180" s="7">
-        <v>358</v>
+        <v>367</v>
       </c>
     </row>
     <row r="181" ht="14.25" customHeight="1">
@@ -7895,7 +7981,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7907,15 +7993,15 @@
         <v>36</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
       <c t="s" r="M181" s="7">
-        <v>359</v>
+        <v>368</v>
       </c>
     </row>
     <row r="182" ht="14.25" customHeight="1">
@@ -7930,7 +8016,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7945,12 +8031,12 @@
         <v>88</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>298</v>
+        <v>304</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -7980,7 +8066,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7992,15 +8078,15 @@
         <v>108</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
       <c t="s" r="M184" s="7">
-        <v>361</v>
+        <v>370</v>
       </c>
     </row>
     <row r="185" ht="15" customHeight="1">
@@ -8015,7 +8101,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -8027,17 +8113,17 @@
         <v>74</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c t="s" r="K185" s="7">
         <v>96</v>
       </c>
       <c r="L185" s="7"/>
       <c t="s" r="M185" s="7">
-        <v>363</v>
+        <v>372</v>
       </c>
     </row>
     <row r="186" ht="14.25" customHeight="1">
@@ -8052,7 +8138,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -8064,7 +8150,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c t="s" r="J186" s="7">
         <v>97</v>
@@ -8072,7 +8158,7 @@
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
       <c t="s" r="M186" s="7">
-        <v>365</v>
+        <v>374</v>
       </c>
     </row>
     <row r="187" ht="14.25" customHeight="1">
@@ -8087,7 +8173,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -8102,12 +8188,12 @@
         <v>120</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
       <c t="s" r="M187" s="7">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="188" ht="14.25" customHeight="1">
@@ -8122,7 +8208,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -8137,12 +8223,12 @@
         <v>47</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
       <c t="s" r="M188" s="7">
-        <v>366</v>
+        <v>375</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
@@ -8157,7 +8243,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -8169,15 +8255,15 @@
         <v>74</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
       <c t="s" r="M189" s="7">
-        <v>367</v>
+        <v>376</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1">
@@ -8207,7 +8293,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -8222,12 +8308,12 @@
         <v>70</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
       <c t="s" r="M191" s="7">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="192" ht="14.25" customHeight="1">
@@ -8242,7 +8328,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -8262,7 +8348,7 @@
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
       <c t="s" r="M192" s="7">
-        <v>369</v>
+        <v>378</v>
       </c>
     </row>
     <row r="193" ht="14.25" customHeight="1">
@@ -8277,7 +8363,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -8292,12 +8378,12 @@
         <v>24</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
       <c t="s" r="M193" s="7">
-        <v>370</v>
+        <v>379</v>
       </c>
     </row>
     <row r="194" ht="14.25" customHeight="1">
@@ -8312,7 +8398,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -8324,10 +8410,10 @@
         <v>95</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -8347,7 +8433,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -8359,15 +8445,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
       <c t="s" r="M195" s="7">
-        <v>371</v>
+        <v>380</v>
       </c>
     </row>
     <row r="196" ht="14.25" customHeight="1">
@@ -8397,7 +8483,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -8409,17 +8495,17 @@
         <v>28</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c t="s" r="J197" s="7">
         <v>41</v>
       </c>
       <c t="s" r="K197" s="7">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="L197" s="7"/>
       <c t="s" r="M197" s="7">
-        <v>373</v>
+        <v>382</v>
       </c>
     </row>
     <row r="198" ht="14.25" customHeight="1">
@@ -8434,7 +8520,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -8443,10 +8529,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H198" s="8">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c t="s" r="J198" s="7">
         <v>59</v>
@@ -8454,7 +8540,7 @@
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
       <c t="s" r="M198" s="7">
-        <v>374</v>
+        <v>383</v>
       </c>
     </row>
     <row r="199" ht="14.25" customHeight="1">
@@ -8469,13 +8555,13 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G199" s="8">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="H199" s="8">
         <v>28</v>
@@ -8489,7 +8575,7 @@
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
       <c t="s" r="M199" s="7">
-        <v>375</v>
+        <v>384</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1">
@@ -8504,7 +8590,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -8526,7 +8612,7 @@
       </c>
       <c r="L200" s="7"/>
       <c t="s" r="M200" s="7">
-        <v>376</v>
+        <v>385</v>
       </c>
     </row>
     <row r="201" ht="14.25" customHeight="1">
@@ -8541,7 +8627,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -8556,14 +8642,14 @@
         <v>89</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c t="s" r="K201" s="7">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="L201" s="7"/>
       <c t="s" r="M201" s="7">
-        <v>379</v>
+        <v>388</v>
       </c>
     </row>
     <row r="202" ht="14.25" customHeight="1">
@@ -8593,7 +8679,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -8605,15 +8691,15 @@
         <v>95</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
       <c t="s" r="M203" s="7">
-        <v>381</v>
+        <v>390</v>
       </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
@@ -8628,7 +8714,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -8640,15 +8726,15 @@
         <v>36</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
       <c t="s" r="M204" s="7">
-        <v>383</v>
+        <v>392</v>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1">
@@ -8663,7 +8749,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8683,7 +8769,7 @@
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
       <c t="s" r="M205" s="7">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="206" ht="14.25" customHeight="1">
@@ -8698,7 +8784,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8710,7 +8796,7 @@
         <v>36</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c t="s" r="J206" s="7">
         <v>47</v>
@@ -8718,7 +8804,7 @@
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
       <c t="s" r="M206" s="7">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="207" ht="14.25" customHeight="1">
@@ -8733,7 +8819,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8742,20 +8828,20 @@
         <v>36</v>
       </c>
       <c t="s" r="H207" s="8">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c t="s" r="J207" s="7">
         <v>109</v>
       </c>
       <c t="s" r="K207" s="7">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="L207" s="7"/>
       <c t="s" r="M207" s="7">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
     <row r="208" ht="14.25" customHeight="1">
@@ -8785,7 +8871,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8797,15 +8883,15 @@
         <v>74</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
       <c t="s" r="M209" s="7">
-        <v>387</v>
+        <v>396</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
@@ -8820,7 +8906,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8829,10 +8915,10 @@
         <v>74</v>
       </c>
       <c t="s" r="H210" s="8">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c t="s" r="J210" s="7">
         <v>77</v>
@@ -8840,7 +8926,7 @@
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
       <c t="s" r="M210" s="7">
-        <v>388</v>
+        <v>397</v>
       </c>
     </row>
     <row r="211" ht="14.25" customHeight="1">
@@ -8855,13 +8941,13 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G211" s="8">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c t="s" r="H211" s="8">
         <v>74</v>
@@ -8875,7 +8961,7 @@
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
       <c t="s" r="M211" s="7">
-        <v>332</v>
+        <v>340</v>
       </c>
     </row>
     <row r="212" ht="14.25" customHeight="1">
@@ -8890,7 +8976,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8899,18 +8985,18 @@
         <v>74</v>
       </c>
       <c t="s" r="H212" s="8">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
       <c t="s" r="M212" s="7">
-        <v>389</v>
+        <v>398</v>
       </c>
     </row>
     <row r="213" ht="14.25" customHeight="1">
@@ -8925,13 +9011,13 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G213" s="8">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="H213" s="8">
         <v>74</v>
@@ -8940,12 +9026,12 @@
         <v>65</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
       <c t="s" r="M213" s="7">
-        <v>391</v>
+        <v>400</v>
       </c>
     </row>
     <row r="214" ht="14.25" customHeight="1">
@@ -8975,27 +9061,27 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G215" s="8">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c t="s" r="H215" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
       <c t="s" r="M215" s="7">
-        <v>395</v>
+        <v>404</v>
       </c>
     </row>
     <row r="216" ht="14.25" customHeight="1">
@@ -9010,7 +9096,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -9019,13 +9105,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H216" s="8">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c t="s" r="I216" s="7">
         <v>33</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -9058,7 +9144,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -9070,17 +9156,17 @@
         <v>36</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c t="s" r="K218" s="7">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="L218" s="7"/>
       <c t="s" r="M218" s="7">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
     <row r="219" ht="14.25" customHeight="1">
@@ -9095,7 +9181,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -9107,7 +9193,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c t="s" r="J219" s="7">
         <v>58</v>
@@ -9130,7 +9216,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -9145,12 +9231,12 @@
         <v>59</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
       <c t="s" r="M220" s="7">
-        <v>398</v>
+        <v>407</v>
       </c>
     </row>
     <row r="221" ht="14.25" customHeight="1">
@@ -9161,11 +9247,11 @@
         <v>8020</v>
       </c>
       <c t="s" r="C221" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -9174,17 +9260,19 @@
         <v>36</v>
       </c>
       <c t="s" r="H221" s="8">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
-      <c r="M221" s="7"/>
+      <c t="s" r="M221" s="7">
+        <v>409</v>
+      </c>
     </row>
     <row r="222" ht="14.25" customHeight="1">
       <c t="s" r="A222" s="6">
@@ -9194,26 +9282,26 @@
         <v>8021</v>
       </c>
       <c t="s" r="C222" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G222" s="8">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c t="s" r="H222" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -9246,7 +9334,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -9255,10 +9343,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H224" s="8">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="J224" s="7">
         <v>54</v>
@@ -9266,7 +9354,7 @@
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
       <c t="s" r="M224" s="7">
-        <v>290</v>
+        <v>296</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1">
@@ -9281,13 +9369,13 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G225" s="8">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c t="s" r="H225" s="8">
         <v>28</v>
@@ -9299,11 +9387,11 @@
         <v>42</v>
       </c>
       <c t="s" r="K225" s="7">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="L225" s="7"/>
       <c t="s" r="M225" s="7">
-        <v>404</v>
+        <v>414</v>
       </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
@@ -9318,7 +9406,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -9327,7 +9415,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H226" s="8">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="I226" s="7">
         <v>45</v>
@@ -9338,7 +9426,7 @@
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
       <c t="s" r="M226" s="7">
-        <v>326</v>
+        <v>334</v>
       </c>
     </row>
     <row r="227" ht="14.25" customHeight="1">
@@ -9353,13 +9441,13 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G227" s="8">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="H227" s="8">
         <v>28</v>
@@ -9373,7 +9461,7 @@
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
       <c t="s" r="M227" s="7">
-        <v>405</v>
+        <v>415</v>
       </c>
     </row>
     <row r="228" ht="14.25" customHeight="1">
@@ -9388,7 +9476,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -9397,20 +9485,20 @@
         <v>28</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c t="s" r="K228" s="7">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="L228" s="7"/>
       <c t="s" r="M228" s="7">
-        <v>409</v>
+        <v>419</v>
       </c>
     </row>
     <row r="229" ht="14.25" customHeight="1">
@@ -9425,22 +9513,22 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c t="s" r="H229" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c t="s" r="K229" s="7">
         <v>18</v>
@@ -9477,7 +9565,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -9486,18 +9574,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H231" s="8">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
       <c t="s" r="M231" s="7">
-        <v>415</v>
+        <v>425</v>
       </c>
     </row>
     <row r="232" ht="14.25" customHeight="1">
@@ -9512,13 +9600,13 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G232" s="8">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c t="s" r="H232" s="8">
         <v>28</v>
@@ -9527,12 +9615,12 @@
         <v>76</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
       <c t="s" r="M232" s="7">
-        <v>416</v>
+        <v>426</v>
       </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
@@ -9547,7 +9635,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -9556,10 +9644,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H233" s="8">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c t="s" r="J233" s="7">
         <v>77</v>
@@ -9567,7 +9655,7 @@
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
       <c t="s" r="M233" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="234" ht="14.25" customHeight="1">
@@ -9582,29 +9670,29 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G234" s="8">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="H234" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c t="s" r="K234" s="7">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="L234" s="7"/>
       <c t="s" r="M234" s="7">
-        <v>419</v>
+        <v>429</v>
       </c>
     </row>
     <row r="235" ht="15" customHeight="1">
@@ -9619,7 +9707,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -9628,18 +9716,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H235" s="8">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
       <c t="s" r="M235" s="7">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="236" ht="14.25" customHeight="1">
@@ -9654,27 +9742,27 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G236" s="8">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="H236" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
       <c t="s" r="M236" s="7">
-        <v>420</v>
+        <v>430</v>
       </c>
     </row>
     <row r="237" ht="14.25" customHeight="1">
@@ -9682,14 +9770,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B237" s="7">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c t="s" r="C237" s="7">
         <v>14</v>
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -9737,7 +9825,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="F239" s="7">
         <v>320</v>
@@ -9749,15 +9837,15 @@
         <v>74</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
       <c t="s" r="M239" s="7">
-        <v>423</v>
+        <v>433</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1">
@@ -9772,7 +9860,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="F240" s="7">
         <v>320</v>
@@ -9781,18 +9869,18 @@
         <v>74</v>
       </c>
       <c t="s" r="H240" s="8">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
       <c t="s" r="M240" s="7">
-        <v>424</v>
+        <v>434</v>
       </c>
     </row>
     <row r="241" ht="14.25" customHeight="1">
@@ -9807,27 +9895,27 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="F241" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G241" s="8">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c t="s" r="H241" s="8">
         <v>74</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
       <c t="s" r="M241" s="7">
-        <v>425</v>
+        <v>435</v>
       </c>
     </row>
     <row r="242" ht="14.25" customHeight="1">
@@ -9842,7 +9930,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="F242" s="7">
         <v>320</v>
@@ -9854,7 +9942,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c t="s" r="J242" s="7">
         <v>58</v>
@@ -9862,7 +9950,7 @@
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
       <c t="s" r="M242" s="7">
-        <v>426</v>
+        <v>436</v>
       </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
@@ -9877,7 +9965,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="F243" s="7">
         <v>320</v>
@@ -9889,15 +9977,15 @@
         <v>74</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
       <c t="s" r="M243" s="7">
-        <v>427</v>
+        <v>437</v>
       </c>
     </row>
     <row r="244" ht="14.25" customHeight="1">
@@ -9912,7 +10000,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="F244" s="7">
         <v>320</v>
@@ -9924,15 +10012,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
       <c t="s" r="M244" s="7">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="245" ht="15" customHeight="1">
@@ -9947,7 +10035,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="F245" s="7">
         <v>320</v>
@@ -9959,14 +10047,16 @@
         <v>74</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
-      <c r="M245" s="7"/>
+      <c t="s" r="M245" s="7">
+        <v>440</v>
+      </c>
     </row>
     <row r="246" ht="14.25" customHeight="1">
       <c r="A246" s="6"/>
@@ -9995,7 +10085,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -10010,14 +10100,14 @@
         <v>96</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c t="s" r="K247" s="7">
         <v>96</v>
       </c>
       <c r="L247" s="7"/>
       <c t="s" r="M247" s="7">
-        <v>431</v>
+        <v>442</v>
       </c>
     </row>
     <row r="248" ht="14.25" customHeight="1">
@@ -10032,7 +10122,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -10044,17 +10134,17 @@
         <v>28</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c t="s" r="J248" s="7">
         <v>123</v>
       </c>
       <c t="s" r="K248" s="7">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="L248" s="7"/>
       <c t="s" r="M248" s="7">
-        <v>304</v>
+        <v>311</v>
       </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
@@ -10069,7 +10159,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -10078,20 +10168,20 @@
         <v>28</v>
       </c>
       <c t="s" r="H249" s="8">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c t="s" r="I249" s="7">
         <v>46</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c t="s" r="K249" s="7">
         <v>47</v>
       </c>
       <c r="L249" s="7"/>
       <c t="s" r="M249" s="7">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1">
@@ -10106,13 +10196,13 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G250" s="8">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c t="s" r="H250" s="8">
         <v>28</v>
@@ -10121,14 +10211,14 @@
         <v>65</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c t="s" r="K250" s="7">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="L250" s="7"/>
       <c t="s" r="M250" s="7">
-        <v>434</v>
+        <v>445</v>
       </c>
     </row>
     <row r="251" ht="14.25" customHeight="1">
@@ -10143,7 +10233,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -10152,17 +10242,19 @@
         <v>28</v>
       </c>
       <c t="s" r="H251" s="8">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c t="s" r="I251" s="7">
         <v>69</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
-      <c r="M251" s="7"/>
+      <c t="s" r="M251" s="7">
+        <v>446</v>
+      </c>
     </row>
     <row r="252" ht="14.25" customHeight="1">
       <c r="A252" s="6"/>
@@ -10191,7 +10283,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="F253" s="7">
         <v>320</v>
@@ -10203,15 +10295,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
       <c t="s" r="M253" s="7">
-        <v>436</v>
+        <v>448</v>
       </c>
     </row>
     <row r="254" ht="14.25" customHeight="1">
@@ -10226,7 +10318,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="F254" s="7">
         <v>320</v>
@@ -10238,17 +10330,17 @@
         <v>74</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c t="s" r="K254" s="7">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="L254" s="7"/>
       <c t="s" r="M254" s="7">
-        <v>437</v>
+        <v>449</v>
       </c>
     </row>
     <row r="255" ht="15" customHeight="1">
@@ -10263,7 +10355,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="F255" s="7">
         <v>320</v>
@@ -10283,7 +10375,7 @@
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
       <c t="s" r="M255" s="7">
-        <v>438</v>
+        <v>450</v>
       </c>
     </row>
     <row r="256" ht="14.25" customHeight="1">
@@ -10298,7 +10390,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="F256" s="7">
         <v>320</v>
@@ -10310,15 +10402,15 @@
         <v>74</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
       <c t="s" r="M256" s="7">
-        <v>439</v>
+        <v>451</v>
       </c>
     </row>
     <row r="257" ht="14.25" customHeight="1">
@@ -10333,7 +10425,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="F257" s="7">
         <v>320</v>
@@ -10342,18 +10434,18 @@
         <v>74</v>
       </c>
       <c t="s" r="H257" s="8">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
       <c t="s" r="M257" s="7">
-        <v>441</v>
+        <v>453</v>
       </c>
     </row>
     <row r="258" ht="14.25" customHeight="1">
@@ -10368,22 +10460,22 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="F258" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G258" s="8">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c t="s" r="H258" s="8">
         <v>74</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -10416,7 +10508,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -10425,18 +10517,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H260" s="8">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c t="s" r="M260" s="7">
-        <v>447</v>
+        <v>459</v>
       </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
@@ -10451,22 +10543,22 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G261" s="8">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c t="s" r="H261" s="8">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="I261" s="7">
         <v>20</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -10486,27 +10578,27 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="H262" s="8">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
       <c t="s" r="M262" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="263" ht="14.25" customHeight="1">
@@ -10521,19 +10613,19 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G263" s="8">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c t="s" r="H263" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c t="s" r="J263" s="7">
         <v>77</v>
@@ -10541,7 +10633,7 @@
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
       <c t="s" r="M263" s="7">
-        <v>448</v>
+        <v>460</v>
       </c>
     </row>
     <row r="264" ht="14.25" customHeight="1">
@@ -10556,7 +10648,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -10565,7 +10657,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="I264" s="7">
         <v>97</v>
@@ -10576,7 +10668,7 @@
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
       <c t="s" r="M264" s="7">
-        <v>449</v>
+        <v>461</v>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1">
@@ -10591,19 +10683,19 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G265" s="8">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="H265" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c t="s" r="J265" s="7">
         <v>125</v>
@@ -10611,7 +10703,7 @@
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
       <c t="s" r="M265" s="7">
-        <v>450</v>
+        <v>462</v>
       </c>
     </row>
     <row r="266" ht="14.25" customHeight="1">
@@ -10641,7 +10733,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="F267" s="7">
         <v>320</v>
@@ -10653,7 +10745,7 @@
         <v>74</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c t="s" r="J267" s="7">
         <v>37</v>
@@ -10661,7 +10753,7 @@
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
       <c t="s" r="M267" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="268" ht="14.25" customHeight="1">
@@ -10676,7 +10768,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="F268" s="7">
         <v>320</v>
@@ -10688,15 +10780,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
       <c t="s" r="M268" s="7">
-        <v>453</v>
+        <v>465</v>
       </c>
     </row>
     <row r="269" ht="14.25" customHeight="1">
@@ -10711,7 +10803,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="F269" s="7">
         <v>320</v>
@@ -10726,12 +10818,12 @@
         <v>24</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
       <c t="s" r="M269" s="7">
-        <v>454</v>
+        <v>466</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1">
@@ -10746,7 +10838,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="F270" s="7">
         <v>320</v>
@@ -10758,15 +10850,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
       <c t="s" r="M270" s="7">
-        <v>455</v>
+        <v>467</v>
       </c>
     </row>
     <row r="271" ht="14.25" customHeight="1">
@@ -10796,7 +10888,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -10805,20 +10897,20 @@
         <v>36</v>
       </c>
       <c t="s" r="H272" s="8">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c t="s" r="I272" s="7">
         <v>38</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c t="s" r="K272" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="L272" s="7"/>
       <c t="s" r="M272" s="7">
-        <v>457</v>
+        <v>469</v>
       </c>
     </row>
     <row r="273" ht="14.25" customHeight="1">
@@ -10833,19 +10925,19 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G273" s="8">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c t="s" r="H273" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c t="s" r="J273" s="7">
         <v>77</v>
@@ -10853,7 +10945,7 @@
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c t="s" r="M273" s="7">
-        <v>458</v>
+        <v>470</v>
       </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
@@ -10868,7 +10960,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -10877,10 +10969,10 @@
         <v>36</v>
       </c>
       <c t="s" r="H274" s="8">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c t="s" r="J274" s="7">
         <v>122</v>
@@ -10888,7 +10980,7 @@
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
       <c t="s" r="M274" s="7">
-        <v>459</v>
+        <v>471</v>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1">
@@ -10903,27 +10995,27 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G275" s="8">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c t="s" r="H275" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
       <c t="s" r="M275" s="7">
-        <v>461</v>
+        <v>473</v>
       </c>
     </row>
     <row r="276" ht="14.25" customHeight="1">
@@ -10938,7 +11030,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -10953,11 +11045,13 @@
         <v>71</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
-      <c r="M276" s="7"/>
+      <c t="s" r="M276" s="7">
+        <v>475</v>
+      </c>
     </row>
     <row r="277" ht="14.25" customHeight="1">
       <c r="A277" s="6"/>
@@ -10986,7 +11080,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="F278" s="7">
         <v>320</v>
@@ -10995,18 +11089,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="I278" s="7">
         <v>70</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
       <c t="s" r="M278" s="7">
-        <v>464</v>
+        <v>477</v>
       </c>
     </row>
     <row r="279" ht="14.25" customHeight="1">
@@ -11021,19 +11115,19 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="H279" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c t="s" r="J279" s="7">
         <v>112</v>
@@ -11041,7 +11135,7 @@
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>466</v>
+        <v>479</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -11056,7 +11150,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
@@ -11065,18 +11159,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H280" s="8">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>436</v>
+        <v>448</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -11091,13 +11185,13 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G281" s="8">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c t="s" r="H281" s="8">
         <v>28</v>
@@ -11106,12 +11200,12 @@
         <v>115</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
       <c t="s" r="M281" s="7">
-        <v>467</v>
+        <v>480</v>
       </c>
     </row>
     <row r="282" ht="14.25" customHeight="1">
@@ -11126,7 +11220,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
@@ -11135,7 +11229,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H282" s="8">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c t="s" r="I282" s="7">
         <v>29</v>
@@ -11146,7 +11240,7 @@
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
       <c t="s" r="M282" s="7">
-        <v>469</v>
+        <v>482</v>
       </c>
     </row>
     <row r="283" ht="14.25" customHeight="1">
@@ -11161,26 +11255,28 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G283" s="8">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c t="s" r="H283" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
-      <c r="M283" s="7"/>
+      <c t="s" r="M283" s="7">
+        <v>483</v>
+      </c>
     </row>
     <row r="284" ht="14.25" customHeight="1">
       <c r="A284" s="6"/>
@@ -11209,7 +11305,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
@@ -11221,15 +11317,15 @@
         <v>74</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
       <c t="s" r="M285" s="7">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="286" ht="14.25" customHeight="1">
@@ -11244,7 +11340,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -11253,13 +11349,13 @@
         <v>74</v>
       </c>
       <c t="s" r="H286" s="8">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c t="s" r="I286" s="7">
         <v>120</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -11279,13 +11375,13 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G287" s="8">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c t="s" r="H287" s="8">
         <v>74</v>
@@ -11294,7 +11390,7 @@
         <v>62</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -11314,7 +11410,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -11323,13 +11419,13 @@
         <v>74</v>
       </c>
       <c t="s" r="H288" s="8">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>471</v>
+        <v>485</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -11362,7 +11458,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>472</v>
+        <v>486</v>
       </c>
       <c r="F290" s="7">
         <v>320</v>
@@ -11382,7 +11478,7 @@
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
       <c t="s" r="M290" s="7">
-        <v>473</v>
+        <v>487</v>
       </c>
     </row>
     <row r="291" ht="14.25" customHeight="1">
@@ -11397,7 +11493,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>472</v>
+        <v>486</v>
       </c>
       <c r="F291" s="7">
         <v>320</v>
@@ -11409,15 +11505,15 @@
         <v>74</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>474</v>
+        <v>488</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
       <c t="s" r="M291" s="7">
-        <v>476</v>
+        <v>490</v>
       </c>
     </row>
     <row r="292" ht="14.25" customHeight="1">
@@ -11432,7 +11528,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>472</v>
+        <v>486</v>
       </c>
       <c r="F292" s="7">
         <v>320</v>
@@ -11441,18 +11537,18 @@
         <v>74</v>
       </c>
       <c t="s" r="H292" s="8">
-        <v>477</v>
+        <v>491</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
       <c t="s" r="M292" s="7">
-        <v>478</v>
+        <v>492</v>
       </c>
     </row>
     <row r="293" ht="14.25" customHeight="1">
@@ -11467,27 +11563,27 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>472</v>
+        <v>486</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G293" s="8">
-        <v>477</v>
+        <v>491</v>
       </c>
       <c t="s" r="H293" s="8">
         <v>74</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
       <c t="s" r="M293" s="7">
-        <v>427</v>
+        <v>437</v>
       </c>
     </row>
     <row r="294" ht="14.25" customHeight="1">
@@ -11517,7 +11613,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>479</v>
+        <v>493</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
@@ -11529,15 +11625,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
       <c t="s" r="M295" s="7">
-        <v>480</v>
+        <v>494</v>
       </c>
     </row>
     <row r="296" ht="14.25" customHeight="1">
@@ -11552,7 +11648,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>479</v>
+        <v>493</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -11564,15 +11660,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
       <c t="s" r="M296" s="7">
-        <v>481</v>
+        <v>495</v>
       </c>
     </row>
     <row r="297" ht="14.25" customHeight="1">
@@ -11587,7 +11683,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>479</v>
+        <v>493</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -11599,17 +11695,17 @@
         <v>28</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c t="s" r="K297" s="7">
         <v>115</v>
       </c>
       <c r="L297" s="7"/>
       <c t="s" r="M297" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="298" ht="14.25" customHeight="1">
@@ -11624,7 +11720,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>479</v>
+        <v>493</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
@@ -11636,17 +11732,17 @@
         <v>74</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c t="s" r="J298" s="7">
         <v>25</v>
       </c>
       <c t="s" r="K298" s="7">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L298" s="7"/>
       <c t="s" r="M298" s="7">
-        <v>482</v>
+        <v>496</v>
       </c>
     </row>
     <row r="299" ht="14.25" customHeight="1">
@@ -11661,7 +11757,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>479</v>
+        <v>493</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
@@ -11673,7 +11769,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c t="s" r="J299" s="7">
         <v>62</v>
@@ -11681,7 +11777,7 @@
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
       <c t="s" r="M299" s="7">
-        <v>427</v>
+        <v>437</v>
       </c>
     </row>
     <row r="300" ht="15" customHeight="1">
@@ -11696,7 +11792,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>479</v>
+        <v>493</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
@@ -11711,12 +11807,12 @@
         <v>126</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
       <c t="s" r="M300" s="7">
-        <v>434</v>
+        <v>445</v>
       </c>
     </row>
     <row r="301" ht="14.25" customHeight="1">
@@ -11746,27 +11842,27 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>483</v>
+        <v>497</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c t="s" r="H302" s="8">
         <v>74</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
       <c t="s" r="M302" s="7">
-        <v>338</v>
+        <v>346</v>
       </c>
     </row>
     <row r="303" ht="14.25" customHeight="1">
@@ -11781,7 +11877,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>483</v>
+        <v>497</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
@@ -11793,15 +11889,15 @@
         <v>36</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
       <c t="s" r="M303" s="7">
-        <v>484</v>
+        <v>498</v>
       </c>
     </row>
     <row r="304" ht="14.25" customHeight="1">
@@ -11816,7 +11912,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>483</v>
+        <v>497</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -11828,15 +11924,15 @@
         <v>74</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
       <c t="s" r="M304" s="7">
-        <v>485</v>
+        <v>499</v>
       </c>
     </row>
     <row r="305" ht="15" customHeight="1">
@@ -11851,7 +11947,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>483</v>
+        <v>497</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -11863,17 +11959,17 @@
         <v>57</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c t="s" r="K305" s="7">
         <v>123</v>
       </c>
       <c r="L305" s="7"/>
       <c t="s" r="M305" s="7">
-        <v>486</v>
+        <v>500</v>
       </c>
     </row>
     <row r="306" ht="14.25" customHeight="1">
@@ -11888,7 +11984,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>483</v>
+        <v>497</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -11900,17 +11996,17 @@
         <v>74</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c t="s" r="J306" s="7">
         <v>86</v>
       </c>
       <c t="s" r="K306" s="7">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="L306" s="7"/>
       <c t="s" r="M306" s="7">
-        <v>353</v>
+        <v>361</v>
       </c>
     </row>
     <row r="307" ht="14.25" customHeight="1">
@@ -11925,7 +12021,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>483</v>
+        <v>497</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
@@ -11937,14 +12033,16 @@
         <v>28</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>487</v>
+        <v>501</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>488</v>
+        <v>502</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
-      <c r="M307" s="7"/>
+      <c t="s" r="M307" s="7">
+        <v>503</v>
+      </c>
     </row>
     <row r="308" ht="14.25" customHeight="1">
       <c r="A308" s="6"/>
@@ -11973,7 +12071,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>489</v>
+        <v>504</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
@@ -11982,18 +12080,18 @@
         <v>74</v>
       </c>
       <c t="s" r="H309" s="8">
-        <v>490</v>
+        <v>505</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>491</v>
+        <v>506</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
       <c t="s" r="M309" s="7">
-        <v>492</v>
+        <v>507</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1">
@@ -12023,7 +12121,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>493</v>
+        <v>508</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -12032,10 +12130,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>494</v>
+        <v>509</v>
       </c>
       <c t="s" r="J311" s="7">
         <v>96</v>
@@ -12043,7 +12141,7 @@
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
       <c t="s" r="M311" s="7">
-        <v>495</v>
+        <v>510</v>
       </c>
     </row>
     <row r="312" ht="14.25" customHeight="1">
@@ -12058,27 +12156,27 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>493</v>
+        <v>508</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="H312" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
       <c t="s" r="M312" s="7">
-        <v>496</v>
+        <v>511</v>
       </c>
     </row>
     <row r="313" ht="14.25" customHeight="1">
@@ -12093,7 +12191,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>493</v>
+        <v>508</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -12102,18 +12200,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>497</v>
+        <v>512</v>
       </c>
       <c t="s" r="I313" s="7">
         <v>78</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
       <c t="s" r="M313" s="7">
-        <v>365</v>
+        <v>374</v>
       </c>
     </row>
     <row r="314" ht="14.25" customHeight="1">
@@ -12128,27 +12226,27 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>493</v>
+        <v>508</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>497</v>
+        <v>512</v>
       </c>
       <c t="s" r="H314" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
       <c t="s" r="M314" s="7">
-        <v>498</v>
+        <v>513</v>
       </c>
     </row>
     <row r="315" ht="15" customHeight="1">
@@ -12163,7 +12261,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>493</v>
+        <v>508</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -12172,18 +12270,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H315" s="8">
-        <v>499</v>
+        <v>514</v>
       </c>
       <c t="s" r="I315" s="7">
         <v>47</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>500</v>
+        <v>515</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c t="s" r="M315" s="7">
-        <v>501</v>
+        <v>516</v>
       </c>
     </row>
     <row r="316" ht="14.25" customHeight="1">
@@ -12198,13 +12296,13 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>493</v>
+        <v>508</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G316" s="8">
-        <v>499</v>
+        <v>514</v>
       </c>
       <c t="s" r="H316" s="8">
         <v>28</v>
@@ -12246,7 +12344,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>502</v>
+        <v>517</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
@@ -12258,7 +12356,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c t="s" r="J318" s="7">
         <v>96</v>
@@ -12266,7 +12364,7 @@
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
       <c t="s" r="M318" s="7">
-        <v>503</v>
+        <v>518</v>
       </c>
     </row>
     <row r="319" ht="14.25" customHeight="1">
@@ -12281,7 +12379,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>502</v>
+        <v>517</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
@@ -12293,15 +12391,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>504</v>
+        <v>519</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
       <c t="s" r="M319" s="7">
-        <v>505</v>
+        <v>520</v>
       </c>
     </row>
     <row r="320" ht="15" customHeight="1">
@@ -12316,7 +12414,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>502</v>
+        <v>517</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
@@ -12325,18 +12423,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c t="s" r="I320" s="7">
         <v>23</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
       <c t="s" r="M320" s="7">
-        <v>506</v>
+        <v>521</v>
       </c>
     </row>
     <row r="321" ht="14.25" customHeight="1">
@@ -12351,19 +12449,19 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>502</v>
+        <v>517</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c t="s" r="H321" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="J321" s="7">
         <v>59</v>
@@ -12371,7 +12469,7 @@
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
       <c t="s" r="M321" s="7">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="322" ht="14.25" customHeight="1">
@@ -12386,7 +12484,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>502</v>
+        <v>517</v>
       </c>
       <c r="F322" s="7">
         <v>321</v>
@@ -12395,20 +12493,20 @@
         <v>28</v>
       </c>
       <c t="s" r="H322" s="8">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c t="s" r="I322" s="7">
         <v>124</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c t="s" r="K322" s="7">
         <v>125</v>
       </c>
       <c r="L322" s="7"/>
       <c t="s" r="M322" s="7">
-        <v>507</v>
+        <v>522</v>
       </c>
     </row>
     <row r="323" ht="14.25" customHeight="1">
@@ -12423,29 +12521,29 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>502</v>
+        <v>517</v>
       </c>
       <c r="F323" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G323" s="8">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c t="s" r="H323" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c t="s" r="K323" s="7">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="L323" s="7"/>
       <c t="s" r="M323" s="7">
-        <v>508</v>
+        <v>523</v>
       </c>
     </row>
     <row r="324" ht="14.25" customHeight="1">
@@ -12475,19 +12573,19 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>509</v>
+        <v>524</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G325" s="8">
-        <v>510</v>
+        <v>525</v>
       </c>
       <c t="s" r="H325" s="8">
         <v>74</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c t="s" r="J325" s="7">
         <v>79</v>
@@ -12495,7 +12593,7 @@
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
       <c t="s" r="M325" s="7">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="326" ht="14.25" customHeight="1">
@@ -12510,7 +12608,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>509</v>
+        <v>524</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -12522,7 +12620,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>511</v>
+        <v>526</v>
       </c>
       <c t="s" r="J326" s="7">
         <v>26</v>
@@ -12530,7 +12628,7 @@
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
       <c t="s" r="M326" s="7">
-        <v>512</v>
+        <v>527</v>
       </c>
     </row>
     <row r="327" ht="14.25" customHeight="1">
@@ -12545,7 +12643,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>509</v>
+        <v>524</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -12557,17 +12655,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c t="s" r="K327" s="7">
         <v>47</v>
       </c>
       <c r="L327" s="7"/>
       <c t="s" r="M327" s="7">
-        <v>513</v>
+        <v>528</v>
       </c>
     </row>
     <row r="328" ht="14.25" customHeight="1">
@@ -12582,7 +12680,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>509</v>
+        <v>524</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
@@ -12594,17 +12692,17 @@
         <v>28</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c t="s" r="J328" s="7">
         <v>67</v>
       </c>
       <c t="s" r="K328" s="7">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="L328" s="7"/>
       <c t="s" r="M328" s="7">
-        <v>353</v>
+        <v>361</v>
       </c>
     </row>
     <row r="329" ht="14.25" customHeight="1">
@@ -12619,7 +12717,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>509</v>
+        <v>524</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -12631,17 +12729,17 @@
         <v>74</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>514</v>
+        <v>529</v>
       </c>
       <c t="s" r="J329" s="7">
         <v>51</v>
       </c>
       <c t="s" r="K329" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L329" s="7"/>
       <c t="s" r="M329" s="7">
-        <v>160</v>
+        <v>530</v>
       </c>
     </row>
     <row r="330" ht="15" customHeight="1">
@@ -12671,7 +12769,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>515</v>
+        <v>531</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -12683,15 +12781,15 @@
         <v>74</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
       <c t="s" r="M331" s="7">
-        <v>516</v>
+        <v>532</v>
       </c>
     </row>
     <row r="332" ht="14.25" customHeight="1">
@@ -12706,7 +12804,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>515</v>
+        <v>531</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
@@ -12718,7 +12816,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c t="s" r="J332" s="7">
         <v>38</v>
@@ -12726,7 +12824,7 @@
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
       <c t="s" r="M332" s="7">
-        <v>517</v>
+        <v>533</v>
       </c>
     </row>
     <row r="333" ht="14.25" customHeight="1">
@@ -12741,7 +12839,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>515</v>
+        <v>531</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -12753,15 +12851,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
       <c t="s" r="M333" s="7">
-        <v>290</v>
+        <v>296</v>
       </c>
     </row>
     <row r="334" ht="14.25" customHeight="1">
@@ -12776,7 +12874,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>515</v>
+        <v>531</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -12796,7 +12894,7 @@
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
       <c t="s" r="M334" s="7">
-        <v>518</v>
+        <v>534</v>
       </c>
     </row>
     <row r="335" ht="15" customHeight="1">
@@ -12811,7 +12909,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>515</v>
+        <v>531</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -12829,11 +12927,11 @@
         <v>62</v>
       </c>
       <c t="s" r="K335" s="7">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="L335" s="7"/>
       <c t="s" r="M335" s="7">
-        <v>519</v>
+        <v>535</v>
       </c>
     </row>
     <row r="336" ht="14.25" customHeight="1">
@@ -12844,11 +12942,11 @@
         <v>40</v>
       </c>
       <c t="s" r="C336" s="7">
-        <v>520</v>
+        <v>536</v>
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>515</v>
+        <v>531</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
@@ -12857,17 +12955,19 @@
         <v>74</v>
       </c>
       <c t="s" r="H336" s="8">
-        <v>521</v>
+        <v>537</v>
       </c>
       <c t="s" r="I336" s="7">
         <v>89</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>522</v>
+        <v>538</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
-      <c r="M336" s="7"/>
+      <c t="s" r="M336" s="7">
+        <v>539</v>
+      </c>
     </row>
     <row r="337" ht="14.25" customHeight="1">
       <c r="A337" s="6"/>
@@ -12896,7 +12996,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>523</v>
+        <v>540</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
@@ -12908,15 +13008,15 @@
         <v>36</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>524</v>
+        <v>541</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -12927,11 +13027,11 @@
         <v>8520</v>
       </c>
       <c t="s" r="C339" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>523</v>
+        <v>540</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
@@ -12940,18 +13040,18 @@
         <v>36</v>
       </c>
       <c t="s" r="H339" s="8">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
       <c t="s" r="M339" s="7">
-        <v>525</v>
+        <v>542</v>
       </c>
     </row>
     <row r="340" ht="15" customHeight="1">
@@ -12962,17 +13062,17 @@
         <v>8521</v>
       </c>
       <c t="s" r="C340" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>523</v>
+        <v>540</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G340" s="8">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c t="s" r="H340" s="8">
         <v>36</v>
@@ -12986,7 +13086,7 @@
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
       <c t="s" r="M340" s="7">
-        <v>526</v>
+        <v>543</v>
       </c>
     </row>
     <row r="341" ht="14.25" customHeight="1">
@@ -13016,7 +13116,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>527</v>
+        <v>544</v>
       </c>
       <c r="F342" s="7">
         <v>321</v>
@@ -13028,15 +13128,15 @@
         <v>74</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>528</v>
+        <v>545</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
       <c t="s" r="M342" s="7">
-        <v>529</v>
+        <v>546</v>
       </c>
     </row>
     <row r="343" ht="14.25" customHeight="1">
@@ -13051,7 +13151,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>527</v>
+        <v>544</v>
       </c>
       <c r="F343" s="7">
         <v>321</v>
@@ -13063,15 +13163,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
       <c t="s" r="M343" s="7">
-        <v>338</v>
+        <v>346</v>
       </c>
     </row>
     <row r="344" ht="14.25" customHeight="1">
@@ -13086,7 +13186,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>527</v>
+        <v>544</v>
       </c>
       <c r="F344" s="7">
         <v>321</v>
@@ -13098,15 +13198,15 @@
         <v>74</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>530</v>
+        <v>547</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c t="s" r="M344" s="7">
-        <v>531</v>
+        <v>548</v>
       </c>
     </row>
     <row r="345" ht="15" customHeight="1">
@@ -13121,7 +13221,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>527</v>
+        <v>544</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
@@ -13133,7 +13233,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c t="s" r="J345" s="7">
         <v>123</v>
@@ -13156,7 +13256,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>527</v>
+        <v>544</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
@@ -13171,14 +13271,14 @@
         <v>46</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c t="s" r="K346" s="7">
         <v>29</v>
       </c>
       <c r="L346" s="7"/>
       <c t="s" r="M346" s="7">
-        <v>507</v>
+        <v>522</v>
       </c>
     </row>
     <row r="347" ht="14.25" customHeight="1">
@@ -13193,7 +13293,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>527</v>
+        <v>544</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
@@ -13202,17 +13302,19 @@
         <v>74</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c t="s" r="I347" s="7">
         <v>130</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
-      <c r="M347" s="7"/>
+      <c t="s" r="M347" s="7">
+        <v>549</v>
+      </c>
     </row>
     <row r="348" ht="14.25" customHeight="1">
       <c t="s" r="A348" s="6">
@@ -13226,22 +13328,22 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>527</v>
+        <v>544</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c t="s" r="H348" s="8">
         <v>74</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>409</v>
+        <v>550</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -13274,7 +13376,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>532</v>
+        <v>551</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
@@ -13289,12 +13391,12 @@
         <v>76</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
       <c t="s" r="M350" s="7">
-        <v>363</v>
+        <v>372</v>
       </c>
     </row>
     <row r="351" ht="14.25" customHeight="1">
@@ -13309,7 +13411,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>532</v>
+        <v>551</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -13321,15 +13423,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
       <c t="s" r="M351" s="7">
-        <v>533</v>
+        <v>552</v>
       </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
@@ -13344,7 +13446,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>532</v>
+        <v>551</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
@@ -13356,15 +13458,15 @@
         <v>36</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>534</v>
+        <v>553</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
       <c t="s" r="M352" s="7">
-        <v>535</v>
+        <v>554</v>
       </c>
     </row>
     <row r="353" ht="14.25" customHeight="1">
@@ -13379,7 +13481,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>532</v>
+        <v>551</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -13391,15 +13493,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
       <c t="s" r="M353" s="7">
-        <v>536</v>
+        <v>555</v>
       </c>
     </row>
     <row r="354" ht="14.25" customHeight="1">
@@ -13414,7 +13516,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>532</v>
+        <v>551</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
@@ -13423,7 +13525,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c t="s" r="I354" s="7">
         <v>67</v>
@@ -13434,7 +13536,7 @@
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
       <c t="s" r="M354" s="7">
-        <v>471</v>
+        <v>485</v>
       </c>
     </row>
     <row r="355" ht="15" customHeight="1">
@@ -13449,22 +13551,22 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>532</v>
+        <v>551</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c t="s" r="H355" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>537</v>
+        <v>556</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>538</v>
+        <v>557</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -13497,7 +13599,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>539</v>
+        <v>558</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -13506,10 +13608,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H357" s="8">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c t="s" r="J357" s="7">
         <v>78</v>
@@ -13517,7 +13619,7 @@
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
       <c t="s" r="M357" s="7">
-        <v>540</v>
+        <v>559</v>
       </c>
     </row>
     <row r="358" ht="14.25" customHeight="1">
@@ -13532,13 +13634,13 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>539</v>
+        <v>558</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G358" s="8">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c t="s" r="H358" s="8">
         <v>28</v>
@@ -13552,7 +13654,7 @@
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
       <c t="s" r="M358" s="7">
-        <v>541</v>
+        <v>560</v>
       </c>
     </row>
     <row r="359" ht="14.25" customHeight="1">
@@ -13567,7 +13669,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>539</v>
+        <v>558</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -13576,7 +13678,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H359" s="8">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="I359" s="7">
         <v>46</v>
@@ -13587,7 +13689,7 @@
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
       <c t="s" r="M359" s="7">
-        <v>542</v>
+        <v>561</v>
       </c>
     </row>
     <row r="360" ht="15" customHeight="1">
@@ -13602,26 +13704,28 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>539</v>
+        <v>558</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G360" s="8">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="H360" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>543</v>
+        <v>562</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>491</v>
+        <v>506</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
-      <c r="M360" s="7"/>
+      <c t="s" r="M360" s="7">
+        <v>84</v>
+      </c>
     </row>
     <row r="361" ht="14.25" customHeight="1">
       <c r="A361" s="6"/>
@@ -13650,7 +13754,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>544</v>
+        <v>563</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -13662,15 +13766,15 @@
         <v>74</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
       <c t="s" r="M362" s="7">
-        <v>495</v>
+        <v>510</v>
       </c>
     </row>
     <row r="363" ht="14.25" customHeight="1">
@@ -13685,7 +13789,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>544</v>
+        <v>563</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -13697,10 +13801,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -13720,7 +13824,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>544</v>
+        <v>563</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -13732,15 +13836,15 @@
         <v>74</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>545</v>
+        <v>564</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
       <c t="s" r="M364" s="7">
-        <v>546</v>
+        <v>565</v>
       </c>
     </row>
     <row r="365" ht="15" customHeight="1">
@@ -13755,7 +13859,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>544</v>
+        <v>563</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -13767,15 +13871,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>547</v>
+        <v>566</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
       <c t="s" r="M365" s="7">
-        <v>398</v>
+        <v>407</v>
       </c>
     </row>
     <row r="366" ht="14.25" customHeight="1">
@@ -13790,7 +13894,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>544</v>
+        <v>563</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
@@ -13805,11 +13909,13 @@
         <v>51</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>548</v>
+        <v>567</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
-      <c r="M366" s="7"/>
+      <c t="s" r="M366" s="7">
+        <v>568</v>
+      </c>
     </row>
     <row r="367" ht="14.25" customHeight="1">
       <c r="A367" s="6"/>
@@ -13838,7 +13944,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>549</v>
+        <v>569</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
@@ -13847,7 +13953,7 @@
         <v>74</v>
       </c>
       <c t="s" r="H368" s="8">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c t="s" r="I368" s="7">
         <v>79</v>
@@ -13860,7 +13966,7 @@
       </c>
       <c r="L368" s="7"/>
       <c t="s" r="M368" s="7">
-        <v>349</v>
+        <v>357</v>
       </c>
     </row>
     <row r="369" ht="14.25" customHeight="1">
@@ -13875,29 +13981,29 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>549</v>
+        <v>569</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G369" s="8">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c t="s" r="H369" s="8">
         <v>74</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c t="s" r="K369" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L369" s="7"/>
       <c t="s" r="M369" s="7">
-        <v>550</v>
+        <v>570</v>
       </c>
     </row>
     <row r="370" ht="15" customHeight="1">
@@ -13912,7 +14018,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>549</v>
+        <v>569</v>
       </c>
       <c r="F370" s="7">
         <v>320</v>
@@ -13921,18 +14027,18 @@
         <v>74</v>
       </c>
       <c t="s" r="H370" s="8">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
       <c t="s" r="M370" s="7">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="371" ht="14.25" customHeight="1">
@@ -13947,26 +14053,28 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>549</v>
+        <v>569</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G371" s="8">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c t="s" r="H371" s="8">
         <v>74</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>551</v>
+        <v>571</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
-      <c r="M371" s="7"/>
+      <c t="s" r="M371" s="7">
+        <v>572</v>
+      </c>
     </row>
     <row r="372" ht="14.25" customHeight="1">
       <c r="A372" s="6"/>
@@ -13995,7 +14103,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>552</v>
+        <v>573</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
@@ -14004,18 +14112,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>530</v>
+        <v>547</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
       <c t="s" r="M373" s="7">
-        <v>341</v>
+        <v>349</v>
       </c>
     </row>
     <row r="374" ht="14.25" customHeight="1">
@@ -14030,27 +14138,27 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>552</v>
+        <v>573</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G374" s="8">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="H374" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
       <c t="s" r="M374" s="7">
-        <v>553</v>
+        <v>574</v>
       </c>
     </row>
     <row r="375" ht="15" customHeight="1">
@@ -14065,7 +14173,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>552</v>
+        <v>573</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
@@ -14074,18 +14182,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H375" s="8">
-        <v>554</v>
+        <v>575</v>
       </c>
       <c t="s" r="I375" s="7">
         <v>102</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>555</v>
+        <v>576</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
       <c t="s" r="M375" s="7">
-        <v>556</v>
+        <v>577</v>
       </c>
     </row>
     <row r="376" ht="14.25" customHeight="1">
@@ -14100,22 +14208,22 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>552</v>
+        <v>573</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G376" s="8">
-        <v>554</v>
+        <v>575</v>
       </c>
       <c t="s" r="H376" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>557</v>
+        <v>578</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -14148,7 +14256,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>558</v>
+        <v>579</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -14168,7 +14276,7 @@
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
       <c t="s" r="M378" s="7">
-        <v>437</v>
+        <v>449</v>
       </c>
     </row>
     <row r="379" ht="14.25" customHeight="1">
@@ -14183,7 +14291,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>558</v>
+        <v>579</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -14192,18 +14300,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H379" s="8">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
       <c t="s" r="M379" s="7">
-        <v>559</v>
+        <v>580</v>
       </c>
     </row>
     <row r="380" ht="15" customHeight="1">
@@ -14218,13 +14326,13 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>558</v>
+        <v>579</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G380" s="8">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c t="s" r="H380" s="8">
         <v>28</v>
@@ -14238,7 +14346,7 @@
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
       <c t="s" r="M380" s="7">
-        <v>282</v>
+        <v>288</v>
       </c>
     </row>
     <row r="381" ht="14.25" customHeight="1">
@@ -14253,7 +14361,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>558</v>
+        <v>579</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -14265,15 +14373,15 @@
         <v>74</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c t="s" r="M381" s="7">
-        <v>560</v>
+        <v>581</v>
       </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
@@ -14303,7 +14411,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>561</v>
+        <v>582</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -14312,20 +14420,20 @@
         <v>28</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c t="s" r="K383" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L383" s="7"/>
       <c t="s" r="M383" s="7">
-        <v>562</v>
+        <v>583</v>
       </c>
     </row>
     <row r="384" ht="14.25" customHeight="1">
@@ -14340,29 +14448,29 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>561</v>
+        <v>582</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="H384" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c t="s" r="K384" s="7">
         <v>96</v>
       </c>
       <c r="L384" s="7"/>
       <c t="s" r="M384" s="7">
-        <v>563</v>
+        <v>584</v>
       </c>
     </row>
     <row r="385" ht="15" customHeight="1">
@@ -14377,7 +14485,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>561</v>
+        <v>582</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -14392,12 +14500,12 @@
         <v>77</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
       <c t="s" r="M385" s="7">
-        <v>531</v>
+        <v>548</v>
       </c>
     </row>
     <row r="386" ht="14.25" customHeight="1">
@@ -14412,7 +14520,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>561</v>
+        <v>582</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
@@ -14427,12 +14535,12 @@
         <v>42</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
       <c t="s" r="M386" s="7">
-        <v>564</v>
+        <v>585</v>
       </c>
     </row>
     <row r="387" ht="14.25" customHeight="1">
@@ -14447,7 +14555,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>561</v>
+        <v>582</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -14459,17 +14567,17 @@
         <v>108</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c t="s" r="K387" s="7">
         <v>61</v>
       </c>
       <c r="L387" s="7"/>
       <c t="s" r="M387" s="7">
-        <v>565</v>
+        <v>586</v>
       </c>
     </row>
     <row r="388" ht="14.25" customHeight="1">
@@ -14484,7 +14592,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>561</v>
+        <v>582</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
@@ -14499,14 +14607,14 @@
         <v>125</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>566</v>
+        <v>587</v>
       </c>
       <c t="s" r="K388" s="7">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="L388" s="7"/>
       <c t="s" r="M388" s="7">
-        <v>567</v>
+        <v>588</v>
       </c>
     </row>
     <row r="389" ht="14.25" customHeight="1">
@@ -14536,7 +14644,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>568</v>
+        <v>589</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
@@ -14548,15 +14656,15 @@
         <v>36</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c t="s" r="M390" s="7">
-        <v>569</v>
+        <v>590</v>
       </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
@@ -14571,7 +14679,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>568</v>
+        <v>589</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
@@ -14583,15 +14691,15 @@
         <v>74</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
       <c t="s" r="M391" s="7">
-        <v>570</v>
+        <v>591</v>
       </c>
     </row>
     <row r="392" ht="14.25" customHeight="1">
@@ -14606,7 +14714,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>568</v>
+        <v>589</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
@@ -14618,17 +14726,17 @@
         <v>28</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c t="s" r="K392" s="7">
         <v>54</v>
       </c>
       <c r="L392" s="7"/>
       <c t="s" r="M392" s="7">
-        <v>571</v>
+        <v>592</v>
       </c>
     </row>
     <row r="393" ht="14.25" customHeight="1">
@@ -14643,7 +14751,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>568</v>
+        <v>589</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
@@ -14652,18 +14760,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H393" s="8">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c t="s" r="I393" s="7">
         <v>120</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
       <c t="s" r="M393" s="7">
-        <v>572</v>
+        <v>593</v>
       </c>
     </row>
     <row r="394" ht="14.25" customHeight="1">
@@ -14678,27 +14786,27 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>568</v>
+        <v>589</v>
       </c>
       <c r="F394" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G394" s="8">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c t="s" r="H394" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
       <c t="s" r="M394" s="7">
-        <v>573</v>
+        <v>594</v>
       </c>
     </row>
     <row r="395" ht="15" customHeight="1">
@@ -14713,7 +14821,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>568</v>
+        <v>589</v>
       </c>
       <c r="F395" s="7">
         <v>320</v>
@@ -14722,7 +14830,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H395" s="8">
-        <v>497</v>
+        <v>512</v>
       </c>
       <c t="s" r="I395" s="7">
         <v>125</v>
@@ -14733,7 +14841,7 @@
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
       <c t="s" r="M395" s="7">
-        <v>574</v>
+        <v>595</v>
       </c>
     </row>
     <row r="396" ht="14.25" customHeight="1">
@@ -14748,27 +14856,27 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>568</v>
+        <v>589</v>
       </c>
       <c r="F396" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G396" s="8">
-        <v>497</v>
+        <v>512</v>
       </c>
       <c t="s" r="H396" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>575</v>
+        <v>596</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
       <c t="s" r="M396" s="7">
-        <v>576</v>
+        <v>597</v>
       </c>
     </row>
     <row r="397" ht="14.25" customHeight="1">
@@ -14794,11 +14902,11 @@
         <v>664</v>
       </c>
       <c t="s" r="C398" s="7">
-        <v>520</v>
+        <v>536</v>
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>577</v>
+        <v>598</v>
       </c>
       <c r="F398" s="7">
         <v>330</v>
@@ -14810,15 +14918,15 @@
         <v>57</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
       <c t="s" r="M398" s="7">
-        <v>578</v>
+        <v>599</v>
       </c>
     </row>
     <row r="399" ht="14.25" customHeight="1">
@@ -14833,7 +14941,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>577</v>
+        <v>598</v>
       </c>
       <c r="F399" s="7">
         <v>330</v>
@@ -14842,18 +14950,18 @@
         <v>57</v>
       </c>
       <c t="s" r="H399" s="8">
-        <v>579</v>
+        <v>600</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
       <c t="s" r="M399" s="7">
-        <v>580</v>
+        <v>601</v>
       </c>
     </row>
     <row r="400" ht="15" customHeight="1">
@@ -14868,26 +14976,28 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>577</v>
+        <v>598</v>
       </c>
       <c r="F400" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G400" s="8">
-        <v>579</v>
+        <v>600</v>
       </c>
       <c t="s" r="H400" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>581</v>
+        <v>602</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
-      <c r="M400" s="7"/>
+      <c t="s" r="M400" s="7">
+        <v>603</v>
+      </c>
     </row>
     <row r="401" ht="14.25" customHeight="1">
       <c r="A401" s="6"/>
@@ -14916,29 +15026,29 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>582</v>
+        <v>604</v>
       </c>
       <c r="F402" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G402" s="8">
-        <v>583</v>
+        <v>605</v>
       </c>
       <c t="s" r="H402" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c t="s" r="K402" s="7">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L402" s="7"/>
       <c t="s" r="M402" s="7">
-        <v>584</v>
+        <v>606</v>
       </c>
     </row>
     <row r="403" ht="14.25" customHeight="1">
@@ -14953,7 +15063,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>582</v>
+        <v>604</v>
       </c>
       <c r="F403" s="7">
         <v>330</v>
@@ -14962,20 +15072,20 @@
         <v>28</v>
       </c>
       <c t="s" r="H403" s="8">
-        <v>585</v>
+        <v>607</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c t="s" r="J403" s="7">
         <v>69</v>
       </c>
       <c t="s" r="K403" s="7">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="L403" s="7"/>
       <c t="s" r="M403" s="7">
-        <v>114</v>
+        <v>137</v>
       </c>
     </row>
     <row r="404" ht="14.25" customHeight="1">
@@ -14990,29 +15100,29 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>582</v>
+        <v>604</v>
       </c>
       <c r="F404" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G404" s="8">
-        <v>585</v>
+        <v>607</v>
       </c>
       <c t="s" r="H404" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c t="s" r="K404" s="7">
-        <v>199</v>
+        <v>227</v>
       </c>
       <c r="L404" s="7"/>
       <c t="s" r="M404" s="7">
-        <v>122</v>
+        <v>158</v>
       </c>
     </row>
     <row r="405" ht="15" customHeight="1">
@@ -15042,7 +15152,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>586</v>
+        <v>608</v>
       </c>
       <c r="F406" s="7">
         <v>330</v>
@@ -15062,7 +15172,7 @@
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>587</v>
+        <v>609</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -15077,7 +15187,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>586</v>
+        <v>608</v>
       </c>
       <c r="F407" s="7">
         <v>330</v>
@@ -15089,15 +15199,15 @@
         <v>57</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
       <c t="s" r="M407" s="7">
-        <v>496</v>
+        <v>511</v>
       </c>
     </row>
     <row r="408" ht="14.25" customHeight="1">
@@ -15112,7 +15222,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>586</v>
+        <v>608</v>
       </c>
       <c r="F408" s="7">
         <v>330</v>
@@ -15121,13 +15231,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H408" s="8">
-        <v>588</v>
+        <v>610</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -15147,26 +15257,28 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>586</v>
+        <v>608</v>
       </c>
       <c r="F409" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>588</v>
+        <v>610</v>
       </c>
       <c t="s" r="H409" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
-      <c r="M409" s="7"/>
+      <c t="s" r="M409" s="7">
+        <v>611</v>
+      </c>
     </row>
     <row r="410" ht="15" customHeight="1">
       <c r="A410" s="6"/>
@@ -15195,13 +15307,13 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>589</v>
+        <v>612</v>
       </c>
       <c r="F411" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G411" s="8">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c t="s" r="H411" s="8">
         <v>74</v>
@@ -15215,7 +15327,7 @@
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
       <c t="s" r="M411" s="7">
-        <v>590</v>
+        <v>613</v>
       </c>
     </row>
     <row r="412" ht="14.25" customHeight="1">
@@ -15230,7 +15342,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>589</v>
+        <v>612</v>
       </c>
       <c r="F412" s="7">
         <v>330</v>
@@ -15242,15 +15354,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>591</v>
+        <v>614</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
       <c t="s" r="M412" s="7">
-        <v>592</v>
+        <v>615</v>
       </c>
     </row>
     <row r="413" ht="14.25" customHeight="1">
@@ -15265,7 +15377,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>589</v>
+        <v>612</v>
       </c>
       <c r="F413" s="7">
         <v>330</v>
@@ -15274,10 +15386,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H413" s="8">
-        <v>583</v>
+        <v>605</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c t="s" r="J413" s="7">
         <v>112</v>
@@ -15287,7 +15399,7 @@
       </c>
       <c r="L413" s="7"/>
       <c t="s" r="M413" s="7">
-        <v>212</v>
+        <v>249</v>
       </c>
     </row>
     <row r="414" ht="14.25" customHeight="1">
@@ -15317,7 +15429,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>593</v>
+        <v>616</v>
       </c>
       <c r="F415" s="7">
         <v>330</v>
@@ -15326,7 +15438,7 @@
         <v>57</v>
       </c>
       <c t="s" r="H415" s="8">
-        <v>594</v>
+        <v>617</v>
       </c>
       <c t="s" r="I415" s="7">
         <v>93</v>
@@ -15337,7 +15449,7 @@
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
       <c t="s" r="M415" s="7">
-        <v>595</v>
+        <v>618</v>
       </c>
     </row>
     <row r="416" ht="14.25" customHeight="1">
@@ -15352,29 +15464,29 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>593</v>
+        <v>616</v>
       </c>
       <c r="F416" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G416" s="8">
-        <v>594</v>
+        <v>617</v>
       </c>
       <c t="s" r="H416" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>596</v>
+        <v>619</v>
       </c>
       <c t="s" r="K416" s="7">
-        <v>500</v>
+        <v>515</v>
       </c>
       <c r="L416" s="7"/>
       <c t="s" r="M416" s="7">
-        <v>149</v>
+        <v>620</v>
       </c>
     </row>
     <row r="417" ht="14.25" customHeight="1">
@@ -15404,7 +15516,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>597</v>
+        <v>621</v>
       </c>
       <c r="F418" s="7">
         <v>330</v>
@@ -15413,20 +15525,20 @@
         <v>28</v>
       </c>
       <c t="s" r="H418" s="8">
-        <v>598</v>
+        <v>622</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c t="s" r="K418" s="7">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="L418" s="7"/>
       <c t="s" r="M418" s="7">
-        <v>599</v>
+        <v>131</v>
       </c>
     </row>
     <row r="419" ht="14.25" customHeight="1">
@@ -15441,34 +15553,34 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>597</v>
+        <v>621</v>
       </c>
       <c r="F419" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G419" s="8">
-        <v>598</v>
+        <v>622</v>
       </c>
       <c t="s" r="H419" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>600</v>
+        <v>577</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c t="s" r="K419" s="7">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="L419" s="7"/>
       <c t="s" r="M419" s="7">
-        <v>601</v>
+        <v>623</v>
       </c>
     </row>
     <row r="420" ht="16.5" customHeight="1">
       <c t="s" r="A420" s="9">
-        <v>602</v>
+        <v>624</v>
       </c>
       <c r="B420" s="9"/>
       <c r="C420" s="9"/>
@@ -15488,7 +15600,7 @@
     <row r="421" ht="65.25" customHeight="1"/>
     <row r="422" ht="16.5" customHeight="1">
       <c t="s" r="A422" s="10">
-        <v>603</v>
+        <v>625</v>
       </c>
       <c r="B422" s="10"/>
       <c r="C422" s="10"/>
@@ -15501,7 +15613,7 @@
       <c r="J422" s="10"/>
       <c r="K422" s="10"/>
       <c t="s" r="L422" s="11">
-        <v>604</v>
+        <v>626</v>
       </c>
       <c r="M422" s="11"/>
       <c r="N422" s="11"/>

--- a/Data/FlightPlan/FPL_08OCT26.xlsx
+++ b/Data/FlightPlan/FPL_08OCT26.xlsx
@@ -641,6 +641,9 @@
     <t>07:10</t>
   </si>
   <si>
+    <t>07:17</t>
+  </si>
+  <si>
     <t>C</t>
   </si>
   <si>
@@ -752,6 +755,9 @@
     <t>09:50</t>
   </si>
   <si>
+    <t>03:55</t>
+  </si>
+  <si>
     <t>VN-A575</t>
   </si>
   <si>
@@ -1175,7 +1181,7 @@
     <t>00:25</t>
   </si>
   <si>
-    <t>01:45</t>
+    <t>02:31</t>
   </si>
   <si>
     <t>VN-A644</t>
@@ -1238,9 +1244,6 @@
     <t>02:40</t>
   </si>
   <si>
-    <t>02:31</t>
-  </si>
-  <si>
     <t>03:35</t>
   </si>
   <si>
@@ -1379,6 +1382,9 @@
     <t>04:50</t>
   </si>
   <si>
+    <t>04:45</t>
+  </si>
+  <si>
     <t>VN-A657</t>
   </si>
   <si>
@@ -1724,9 +1730,6 @@
     <t>18:18</t>
   </si>
   <si>
-    <t>03:55</t>
-  </si>
-  <si>
     <t>04:00</t>
   </si>
   <si>
@@ -1886,7 +1889,7 @@
     <t>Total Record(s): 342</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 09, 2026 00:50</t>
+    <t xml:space="preserve">Generated on  Oct 09, 2026 01:18</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -4857,7 +4860,9 @@
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
-      <c r="M82" s="7"/>
+      <c t="s" r="M82" s="7">
+        <v>210</v>
+      </c>
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c r="A83" s="6"/>
@@ -4882,33 +4887,33 @@
         <v>3524</v>
       </c>
       <c t="s" r="C84" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G84" s="8">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="H84" s="8">
         <v>74</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c t="s" r="K84" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L84" s="7"/>
       <c t="s" r="M84" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
@@ -4919,11 +4924,11 @@
         <v>3524</v>
       </c>
       <c t="s" r="C85" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
@@ -4935,7 +4940,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c t="s" r="J85" s="7">
         <v>58</v>
@@ -4945,7 +4950,7 @@
       </c>
       <c r="L85" s="7"/>
       <c t="s" r="M85" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
@@ -4960,7 +4965,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4975,14 +4980,14 @@
         <v>125</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="K86" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L86" s="7"/>
       <c t="s" r="M86" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="87" ht="14.25" customHeight="1">
@@ -5012,7 +5017,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -5024,7 +5029,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c t="s" r="J88" s="7">
         <v>180</v>
@@ -5034,7 +5039,7 @@
       </c>
       <c r="L88" s="7"/>
       <c t="s" r="M88" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="89" ht="14.25" customHeight="1">
@@ -5049,7 +5054,7 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -5069,7 +5074,7 @@
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
       <c t="s" r="M89" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1">
@@ -5099,7 +5104,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -5111,15 +5116,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
       <c t="s" r="M91" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="92" ht="14.25" customHeight="1">
@@ -5134,7 +5139,7 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -5143,20 +5148,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H92" s="8">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="J92" s="7">
         <v>121</v>
       </c>
       <c t="s" r="K92" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L92" s="7"/>
       <c t="s" r="M92" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="93" ht="14.25" customHeight="1">
@@ -5171,29 +5176,29 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G93" s="8">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="H93" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="J93" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="K93" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="L93" s="7"/>
       <c t="s" r="M93" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="94" ht="14.25" customHeight="1">
@@ -5208,7 +5213,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -5230,7 +5235,7 @@
       </c>
       <c r="L94" s="7"/>
       <c t="s" r="M94" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
@@ -5245,7 +5250,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -5257,13 +5262,13 @@
         <v>16</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c t="s" r="J95" s="7">
         <v>152</v>
       </c>
       <c t="s" r="K95" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L95" s="7"/>
       <c t="s" r="M95" s="7">
@@ -5293,11 +5298,11 @@
         <v>7621</v>
       </c>
       <c t="s" r="C97" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -5317,7 +5322,7 @@
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
       <c t="s" r="M97" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
@@ -5332,7 +5337,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -5347,12 +5352,12 @@
         <v>97</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
       <c t="s" r="M98" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="99" ht="14.25" customHeight="1">
@@ -5367,7 +5372,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -5387,7 +5392,7 @@
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
       <c t="s" r="M99" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1">
@@ -5402,7 +5407,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -5414,14 +5419,18 @@
         <v>207</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>246</v>
-      </c>
-      <c r="K100" s="7"/>
+        <v>247</v>
+      </c>
+      <c t="s" r="K100" s="7">
+        <v>248</v>
+      </c>
       <c r="L100" s="7"/>
-      <c r="M100" s="7"/>
+      <c t="s" r="M100" s="7">
+        <v>38</v>
+      </c>
     </row>
     <row r="101" ht="14.25" customHeight="1">
       <c r="A101" s="6"/>
@@ -5450,7 +5459,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -5462,17 +5471,17 @@
         <v>28</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c t="s" r="K102" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L102" s="7"/>
       <c t="s" r="M102" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="103" ht="14.25" customHeight="1">
@@ -5487,7 +5496,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -5499,7 +5508,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="J103" s="7">
         <v>124</v>
@@ -5507,7 +5516,7 @@
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
       <c t="s" r="M103" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="104" ht="14.25" customHeight="1">
@@ -5522,7 +5531,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -5537,12 +5546,12 @@
         <v>191</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
       <c t="s" r="M104" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
@@ -5572,7 +5581,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -5584,10 +5593,10 @@
         <v>74</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -5607,7 +5616,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -5616,18 +5625,18 @@
         <v>74</v>
       </c>
       <c t="s" r="H107" s="8">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
       <c t="s" r="M107" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
     <row r="108" ht="14.25" customHeight="1">
@@ -5642,13 +5651,13 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G108" s="8">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c t="s" r="H108" s="8">
         <v>74</v>
@@ -5657,14 +5666,14 @@
         <v>124</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="K108" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L108" s="7"/>
       <c t="s" r="M108" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="109" ht="14.25" customHeight="1">
@@ -5679,7 +5688,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -5691,7 +5700,7 @@
         <v>32</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="J109" s="7">
         <v>110</v>
@@ -5727,13 +5736,13 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G111" s="8">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c t="s" r="H111" s="8">
         <v>74</v>
@@ -5742,12 +5751,12 @@
         <v>152</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
       <c t="s" r="M111" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="112" ht="14.25" customHeight="1">
@@ -5762,7 +5771,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5793,11 +5802,11 @@
         <v>7614</v>
       </c>
       <c t="s" r="C113" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5812,7 +5821,7 @@
         <v>103</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -5828,11 +5837,11 @@
         <v>7614</v>
       </c>
       <c t="s" r="C114" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5841,10 +5850,10 @@
         <v>74</v>
       </c>
       <c t="s" r="H114" s="8">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c t="s" r="J114" s="7">
         <v>22</v>
@@ -5880,7 +5889,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5900,7 +5909,7 @@
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
       <c t="s" r="M116" s="7">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
@@ -5915,7 +5924,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5924,10 +5933,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H117" s="8">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="J117" s="7">
         <v>33</v>
@@ -5935,7 +5944,7 @@
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
       <c t="s" r="M117" s="7">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
@@ -5950,27 +5959,27 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G118" s="8">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c t="s" r="H118" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
       <c t="s" r="M118" s="7">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="119" ht="14.25" customHeight="1">
@@ -6000,7 +6009,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -6012,17 +6021,17 @@
         <v>57</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c t="s" r="J120" s="7">
         <v>174</v>
       </c>
       <c t="s" r="K120" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L120" s="7"/>
       <c t="s" r="M120" s="7">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="121" ht="14.25" customHeight="1">
@@ -6037,7 +6046,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -6057,7 +6066,7 @@
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
       <c t="s" r="M121" s="7">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="122" ht="14.25" customHeight="1">
@@ -6087,7 +6096,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -6102,12 +6111,12 @@
         <v>113</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
       <c t="s" r="M123" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="124" ht="14.25" customHeight="1">
@@ -6122,7 +6131,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -6134,7 +6143,7 @@
         <v>36</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c t="s" r="J124" s="7">
         <v>171</v>
@@ -6142,7 +6151,7 @@
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
       <c t="s" r="M124" s="7">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1">
@@ -6157,7 +6166,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -6172,14 +6181,14 @@
         <v>155</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c t="s" r="K125" s="7">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="L125" s="7"/>
       <c t="s" r="M125" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="126" ht="14.25" customHeight="1">
@@ -6194,7 +6203,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -6206,7 +6215,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c t="s" r="J126" s="7">
         <v>191</v>
@@ -6216,7 +6225,7 @@
       </c>
       <c r="L126" s="7"/>
       <c t="s" r="M126" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
@@ -6246,7 +6255,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -6258,15 +6267,15 @@
         <v>203</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
       <c t="s" r="M128" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="129" ht="14.25" customHeight="1">
@@ -6281,7 +6290,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -6293,15 +6302,15 @@
         <v>74</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
       <c t="s" r="M129" s="7">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1">
@@ -6316,7 +6325,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -6328,7 +6337,7 @@
         <v>185</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c t="s" r="J130" s="7">
         <v>171</v>
@@ -6336,7 +6345,7 @@
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
       <c t="s" r="M130" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="131" ht="14.25" customHeight="1">
@@ -6351,7 +6360,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -6371,7 +6380,7 @@
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
       <c t="s" r="M131" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="132" ht="14.25" customHeight="1">
@@ -6386,7 +6395,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -6395,20 +6404,20 @@
         <v>74</v>
       </c>
       <c t="s" r="H132" s="8">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="I132" s="7">
         <v>121</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c t="s" r="K132" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L132" s="7"/>
       <c t="s" r="M132" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="133" ht="14.25" customHeight="1">
@@ -6423,13 +6432,13 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G133" s="8">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="H133" s="8">
         <v>74</v>
@@ -6438,7 +6447,7 @@
         <v>46</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c t="s" r="K133" s="7">
         <v>47</v>
@@ -6460,7 +6469,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -6475,12 +6484,12 @@
         <v>86</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
       <c t="s" r="M134" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1">
@@ -6495,7 +6504,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -6510,12 +6519,12 @@
         <v>89</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
       <c t="s" r="M135" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="136" ht="14.25" customHeight="1">
@@ -6545,7 +6554,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -6554,20 +6563,20 @@
         <v>28</v>
       </c>
       <c t="s" r="H137" s="8">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c t="s" r="J137" s="7">
         <v>174</v>
       </c>
       <c t="s" r="K137" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L137" s="7"/>
       <c t="s" r="M137" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="138" ht="14.25" customHeight="1">
@@ -6582,13 +6591,13 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G138" s="8">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c t="s" r="H138" s="8">
         <v>28</v>
@@ -6600,11 +6609,11 @@
         <v>99</v>
       </c>
       <c t="s" r="K138" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L138" s="7"/>
       <c t="s" r="M138" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="139" ht="14.25" customHeight="1">
@@ -6619,7 +6628,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -6628,18 +6637,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H139" s="8">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
       <c t="s" r="M139" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="140" ht="15" customHeight="1">
@@ -6654,22 +6663,22 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G140" s="8">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c t="s" r="H140" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
@@ -6702,7 +6711,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -6714,7 +6723,7 @@
         <v>201</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c t="s" r="J142" s="7">
         <v>171</v>
@@ -6722,7 +6731,7 @@
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
       <c t="s" r="M142" s="7">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
@@ -6737,7 +6746,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6752,12 +6761,12 @@
         <v>24</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
       <c t="s" r="M143" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="144" ht="14.25" customHeight="1">
@@ -6772,7 +6781,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -6787,12 +6796,12 @@
         <v>142</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
       <c t="s" r="M144" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1">
@@ -6807,7 +6816,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6822,12 +6831,12 @@
         <v>164</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
       <c t="s" r="M145" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="146" ht="14.25" customHeight="1">
@@ -6842,7 +6851,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6854,7 +6863,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c t="s" r="J146" s="7">
         <v>66</v>
@@ -6862,7 +6871,7 @@
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -6892,7 +6901,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6904,7 +6913,7 @@
         <v>201</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c t="s" r="J148" s="7">
         <v>135</v>
@@ -6912,7 +6921,7 @@
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
       <c t="s" r="M148" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="149" ht="14.25" customHeight="1">
@@ -6927,7 +6936,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6947,7 +6956,7 @@
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
       <c t="s" r="M149" s="7">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="150" ht="15" customHeight="1">
@@ -6962,7 +6971,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6971,13 +6980,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H150" s="8">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="I150" s="7">
         <v>202</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6997,19 +7006,19 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G151" s="8">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="H151" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c t="s" r="J151" s="7">
         <v>173</v>
@@ -7017,7 +7026,7 @@
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
       <c t="s" r="M151" s="7">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="152" ht="14.25" customHeight="1">
@@ -7032,7 +7041,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -7067,7 +7076,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -7082,12 +7091,12 @@
         <v>178</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
       <c t="s" r="M153" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="154" ht="14.25" customHeight="1">
@@ -7102,7 +7111,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -7114,15 +7123,15 @@
         <v>36</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
       <c t="s" r="M154" s="7">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
@@ -7137,7 +7146,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -7149,10 +7158,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -7187,7 +7196,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -7196,18 +7205,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H157" s="8">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c t="s" r="I157" s="7">
         <v>168</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
       <c t="s" r="M157" s="7">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="158" ht="14.25" customHeight="1">
@@ -7222,13 +7231,13 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G158" s="8">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c t="s" r="H158" s="8">
         <v>28</v>
@@ -7237,12 +7246,12 @@
         <v>38</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
       <c t="s" r="M158" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="159" ht="14.25" customHeight="1">
@@ -7257,7 +7266,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -7277,7 +7286,7 @@
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
       <c t="s" r="M159" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="160" ht="15" customHeight="1">
@@ -7292,7 +7301,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -7304,15 +7313,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
       <c t="s" r="M160" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
@@ -7342,7 +7351,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -7351,18 +7360,18 @@
         <v>74</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c t="s" r="I162" s="7">
         <v>149</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
       <c t="s" r="M162" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="163" ht="14.25" customHeight="1">
@@ -7377,29 +7386,29 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c t="s" r="H163" s="8">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c t="s" r="K163" s="7">
         <v>96</v>
       </c>
       <c r="L163" s="7"/>
       <c t="s" r="M163" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="164" ht="14.25" customHeight="1">
@@ -7414,19 +7423,19 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G164" s="8">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c t="s" r="H164" s="8">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="J164" s="7">
         <v>24</v>
@@ -7436,7 +7445,7 @@
       </c>
       <c r="L164" s="7"/>
       <c t="s" r="M164" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1">
@@ -7451,13 +7460,13 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G165" s="8">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c t="s" r="H165" s="8">
         <v>74</v>
@@ -7488,7 +7497,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -7497,10 +7506,10 @@
         <v>74</v>
       </c>
       <c t="s" r="H166" s="8">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c t="s" r="J166" s="7">
         <v>164</v>
@@ -7510,7 +7519,7 @@
       </c>
       <c r="L166" s="7"/>
       <c t="s" r="M166" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="167" ht="14.25" customHeight="1">
@@ -7525,13 +7534,13 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G167" s="8">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c t="s" r="H167" s="8">
         <v>74</v>
@@ -7543,11 +7552,11 @@
         <v>86</v>
       </c>
       <c t="s" r="K167" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L167" s="7"/>
       <c t="s" r="M167" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="168" ht="14.25" customHeight="1">
@@ -7562,7 +7571,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -7574,7 +7583,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c t="s" r="J168" s="7">
         <v>69</v>
@@ -7582,7 +7591,7 @@
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
       <c t="s" r="M168" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="169" ht="14.25" customHeight="1">
@@ -7612,7 +7621,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -7627,12 +7636,12 @@
         <v>134</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
       <c t="s" r="M170" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="171" ht="14.25" customHeight="1">
@@ -7647,7 +7656,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -7656,18 +7665,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H171" s="8">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c t="s" r="I171" s="7">
         <v>22</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
       <c t="s" r="M171" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="172" ht="14.25" customHeight="1">
@@ -7682,19 +7691,19 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G172" s="8">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c t="s" r="H172" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="J172" s="7">
         <v>77</v>
@@ -7717,7 +7726,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -7726,7 +7735,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c t="s" r="I173" s="7">
         <v>79</v>
@@ -7737,7 +7746,7 @@
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
       <c t="s" r="M173" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="174" ht="14.25" customHeight="1">
@@ -7752,13 +7761,13 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G174" s="8">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c t="s" r="H174" s="8">
         <v>28</v>
@@ -7767,12 +7776,12 @@
         <v>144</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
       <c t="s" r="M174" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1">
@@ -7787,7 +7796,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -7799,17 +7808,17 @@
         <v>74</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c t="s" r="J175" s="7">
         <v>192</v>
       </c>
       <c t="s" r="K175" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L175" s="7"/>
       <c t="s" r="M175" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
@@ -7824,7 +7833,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7839,14 +7848,14 @@
         <v>192</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c t="s" r="K176" s="7">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="L176" s="7"/>
       <c t="s" r="M176" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
@@ -7876,13 +7885,13 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G178" s="8">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c t="s" r="H178" s="8">
         <v>74</v>
@@ -7891,7 +7900,7 @@
         <v>187</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -7911,7 +7920,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7931,7 +7940,7 @@
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
       <c t="s" r="M179" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1">
@@ -7946,7 +7955,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7966,7 +7975,7 @@
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
       <c t="s" r="M180" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="181" ht="14.25" customHeight="1">
@@ -7981,7 +7990,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7993,15 +8002,15 @@
         <v>36</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
       <c t="s" r="M181" s="7">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="182" ht="14.25" customHeight="1">
@@ -8016,7 +8025,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -8036,7 +8045,7 @@
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -8066,7 +8075,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -8081,12 +8090,12 @@
         <v>209</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
       <c t="s" r="M184" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="185" ht="15" customHeight="1">
@@ -8101,7 +8110,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -8113,17 +8122,17 @@
         <v>74</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c t="s" r="K185" s="7">
         <v>96</v>
       </c>
       <c r="L185" s="7"/>
       <c t="s" r="M185" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="186" ht="14.25" customHeight="1">
@@ -8138,7 +8147,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -8150,7 +8159,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c t="s" r="J186" s="7">
         <v>97</v>
@@ -8158,7 +8167,7 @@
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
       <c t="s" r="M186" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="187" ht="14.25" customHeight="1">
@@ -8173,7 +8182,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -8188,12 +8197,12 @@
         <v>120</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
       <c t="s" r="M187" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="188" ht="14.25" customHeight="1">
@@ -8208,7 +8217,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -8223,12 +8232,12 @@
         <v>47</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
       <c t="s" r="M188" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
@@ -8243,7 +8252,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -8255,15 +8264,15 @@
         <v>74</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
       <c t="s" r="M189" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1">
@@ -8293,7 +8302,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -8328,7 +8337,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -8348,7 +8357,7 @@
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
       <c t="s" r="M192" s="7">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="193" ht="14.25" customHeight="1">
@@ -8363,7 +8372,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -8378,12 +8387,12 @@
         <v>24</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
       <c t="s" r="M193" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="194" ht="14.25" customHeight="1">
@@ -8398,7 +8407,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -8413,7 +8422,7 @@
         <v>158</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -8433,7 +8442,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -8445,15 +8454,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
       <c t="s" r="M195" s="7">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="196" ht="14.25" customHeight="1">
@@ -8483,7 +8492,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -8495,17 +8504,17 @@
         <v>28</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c t="s" r="J197" s="7">
         <v>41</v>
       </c>
       <c t="s" r="K197" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="L197" s="7"/>
       <c t="s" r="M197" s="7">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="198" ht="14.25" customHeight="1">
@@ -8520,7 +8529,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -8540,7 +8549,7 @@
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
       <c t="s" r="M198" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="199" ht="14.25" customHeight="1">
@@ -8555,7 +8564,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -8575,7 +8584,7 @@
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
       <c t="s" r="M199" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1">
@@ -8590,7 +8599,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -8612,7 +8621,7 @@
       </c>
       <c r="L200" s="7"/>
       <c t="s" r="M200" s="7">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="201" ht="14.25" customHeight="1">
@@ -8627,7 +8636,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -8642,14 +8651,14 @@
         <v>89</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c t="s" r="K201" s="7">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="L201" s="7"/>
       <c t="s" r="M201" s="7">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="202" ht="14.25" customHeight="1">
@@ -8679,7 +8688,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -8699,7 +8708,7 @@
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
       <c t="s" r="M203" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
@@ -8714,7 +8723,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -8726,7 +8735,7 @@
         <v>36</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c t="s" r="J204" s="7">
         <v>155</v>
@@ -8734,7 +8743,7 @@
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
       <c t="s" r="M204" s="7">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1">
@@ -8749,7 +8758,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8784,7 +8793,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8796,7 +8805,7 @@
         <v>36</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="J206" s="7">
         <v>47</v>
@@ -8819,7 +8828,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8837,11 +8846,11 @@
         <v>109</v>
       </c>
       <c t="s" r="K207" s="7">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L207" s="7"/>
       <c t="s" r="M207" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="208" ht="14.25" customHeight="1">
@@ -8871,7 +8880,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8883,7 +8892,7 @@
         <v>74</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c t="s" r="J209" s="7">
         <v>187</v>
@@ -8891,7 +8900,7 @@
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
       <c t="s" r="M209" s="7">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
@@ -8906,7 +8915,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8915,10 +8924,10 @@
         <v>74</v>
       </c>
       <c t="s" r="H210" s="8">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="J210" s="7">
         <v>77</v>
@@ -8926,7 +8935,7 @@
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
       <c t="s" r="M210" s="7">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="211" ht="14.25" customHeight="1">
@@ -8941,13 +8950,13 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G211" s="8">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c t="s" r="H211" s="8">
         <v>74</v>
@@ -8961,7 +8970,7 @@
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
       <c t="s" r="M211" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="212" ht="14.25" customHeight="1">
@@ -8976,7 +8985,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8988,15 +8997,15 @@
         <v>201</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
       <c t="s" r="M212" s="7">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="213" ht="14.25" customHeight="1">
@@ -9011,7 +9020,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -9026,12 +9035,12 @@
         <v>65</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
       <c t="s" r="M213" s="7">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="214" ht="14.25" customHeight="1">
@@ -9061,27 +9070,27 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G215" s="8">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c t="s" r="H215" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
       <c t="s" r="M215" s="7">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="216" ht="14.25" customHeight="1">
@@ -9096,7 +9105,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -9105,7 +9114,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H216" s="8">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c t="s" r="I216" s="7">
         <v>33</v>
@@ -9144,7 +9153,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -9159,14 +9168,14 @@
         <v>135</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c t="s" r="K218" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L218" s="7"/>
       <c t="s" r="M218" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="219" ht="14.25" customHeight="1">
@@ -9181,7 +9190,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -9193,7 +9202,7 @@
         <v>21</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c t="s" r="J219" s="7">
         <v>58</v>
@@ -9216,7 +9225,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -9236,7 +9245,7 @@
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
       <c t="s" r="M220" s="7">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="221" ht="14.25" customHeight="1">
@@ -9247,11 +9256,11 @@
         <v>8020</v>
       </c>
       <c t="s" r="C221" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -9260,18 +9269,18 @@
         <v>36</v>
       </c>
       <c t="s" r="H221" s="8">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
       <c t="s" r="M221" s="7">
-        <v>409</v>
+        <v>390</v>
       </c>
     </row>
     <row r="222" ht="14.25" customHeight="1">
@@ -9282,26 +9291,26 @@
         <v>8021</v>
       </c>
       <c t="s" r="C222" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G222" s="8">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c t="s" r="H222" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -9334,7 +9343,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -9343,7 +9352,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H224" s="8">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c t="s" r="I224" s="7">
         <v>135</v>
@@ -9354,7 +9363,7 @@
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
       <c t="s" r="M224" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1">
@@ -9369,13 +9378,13 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G225" s="8">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c t="s" r="H225" s="8">
         <v>28</v>
@@ -9387,11 +9396,11 @@
         <v>42</v>
       </c>
       <c t="s" r="K225" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="L225" s="7"/>
       <c t="s" r="M225" s="7">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
@@ -9406,7 +9415,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -9426,7 +9435,7 @@
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
       <c t="s" r="M226" s="7">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="227" ht="14.25" customHeight="1">
@@ -9441,7 +9450,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -9461,7 +9470,7 @@
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
       <c t="s" r="M227" s="7">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="228" ht="14.25" customHeight="1">
@@ -9476,7 +9485,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -9485,20 +9494,20 @@
         <v>28</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c t="s" r="K228" s="7">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L228" s="7"/>
       <c t="s" r="M228" s="7">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="229" ht="14.25" customHeight="1">
@@ -9513,22 +9522,22 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c t="s" r="H229" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c t="s" r="K229" s="7">
         <v>18</v>
@@ -9565,7 +9574,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -9574,18 +9583,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H231" s="8">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
       <c t="s" r="M231" s="7">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="232" ht="14.25" customHeight="1">
@@ -9600,13 +9609,13 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G232" s="8">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c t="s" r="H232" s="8">
         <v>28</v>
@@ -9620,7 +9629,7 @@
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
       <c t="s" r="M232" s="7">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
@@ -9635,7 +9644,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -9647,7 +9656,7 @@
         <v>133</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c t="s" r="J233" s="7">
         <v>77</v>
@@ -9670,7 +9679,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -9682,17 +9691,17 @@
         <v>28</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c t="s" r="K234" s="7">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L234" s="7"/>
       <c t="s" r="M234" s="7">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="235" ht="15" customHeight="1">
@@ -9707,7 +9716,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -9719,15 +9728,15 @@
         <v>201</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
       <c t="s" r="M235" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="236" ht="14.25" customHeight="1">
@@ -9742,7 +9751,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -9757,12 +9766,12 @@
         <v>180</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
       <c t="s" r="M236" s="7">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="237" ht="14.25" customHeight="1">
@@ -9770,14 +9779,14 @@
         <v>13</v>
       </c>
       <c t="s" r="B237" s="7">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c t="s" r="C237" s="7">
         <v>14</v>
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -9825,7 +9834,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F239" s="7">
         <v>320</v>
@@ -9840,12 +9849,12 @@
         <v>135</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
       <c t="s" r="M239" s="7">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1">
@@ -9860,7 +9869,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F240" s="7">
         <v>320</v>
@@ -9869,18 +9878,18 @@
         <v>74</v>
       </c>
       <c t="s" r="H240" s="8">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
       <c t="s" r="M240" s="7">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="241" ht="14.25" customHeight="1">
@@ -9895,27 +9904,27 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F241" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G241" s="8">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="H241" s="8">
         <v>74</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
       <c t="s" r="M241" s="7">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="242" ht="14.25" customHeight="1">
@@ -9930,7 +9939,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F242" s="7">
         <v>320</v>
@@ -9942,7 +9951,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c t="s" r="J242" s="7">
         <v>58</v>
@@ -9950,7 +9959,7 @@
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
       <c t="s" r="M242" s="7">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
@@ -9965,7 +9974,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F243" s="7">
         <v>320</v>
@@ -9977,15 +9986,15 @@
         <v>74</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
       <c t="s" r="M243" s="7">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="244" ht="14.25" customHeight="1">
@@ -10000,7 +10009,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F244" s="7">
         <v>320</v>
@@ -10012,15 +10021,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
       <c t="s" r="M244" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="245" ht="15" customHeight="1">
@@ -10035,7 +10044,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F245" s="7">
         <v>320</v>
@@ -10047,15 +10056,15 @@
         <v>74</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
       <c t="s" r="M245" s="7">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="246" ht="14.25" customHeight="1">
@@ -10085,7 +10094,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -10100,14 +10109,14 @@
         <v>96</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c t="s" r="K247" s="7">
         <v>96</v>
       </c>
       <c r="L247" s="7"/>
       <c t="s" r="M247" s="7">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="248" ht="14.25" customHeight="1">
@@ -10122,7 +10131,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -10134,17 +10143,17 @@
         <v>28</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="J248" s="7">
         <v>123</v>
       </c>
       <c t="s" r="K248" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="L248" s="7"/>
       <c t="s" r="M248" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
@@ -10159,7 +10168,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -10168,20 +10177,20 @@
         <v>28</v>
       </c>
       <c t="s" r="H249" s="8">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c t="s" r="I249" s="7">
         <v>46</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c t="s" r="K249" s="7">
         <v>47</v>
       </c>
       <c r="L249" s="7"/>
       <c t="s" r="M249" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1">
@@ -10196,13 +10205,13 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G250" s="8">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c t="s" r="H250" s="8">
         <v>28</v>
@@ -10211,14 +10220,14 @@
         <v>65</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c t="s" r="K250" s="7">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L250" s="7"/>
       <c t="s" r="M250" s="7">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="251" ht="14.25" customHeight="1">
@@ -10233,7 +10242,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -10253,7 +10262,7 @@
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
       <c t="s" r="M251" s="7">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="252" ht="14.25" customHeight="1">
@@ -10283,7 +10292,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F253" s="7">
         <v>320</v>
@@ -10295,15 +10304,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
       <c t="s" r="M253" s="7">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="254" ht="14.25" customHeight="1">
@@ -10318,7 +10327,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F254" s="7">
         <v>320</v>
@@ -10330,17 +10339,17 @@
         <v>74</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="K254" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L254" s="7"/>
       <c t="s" r="M254" s="7">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="255" ht="15" customHeight="1">
@@ -10355,7 +10364,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F255" s="7">
         <v>320</v>
@@ -10375,7 +10384,7 @@
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
       <c t="s" r="M255" s="7">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="256" ht="14.25" customHeight="1">
@@ -10390,7 +10399,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F256" s="7">
         <v>320</v>
@@ -10402,15 +10411,15 @@
         <v>74</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
       <c t="s" r="M256" s="7">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="257" ht="14.25" customHeight="1">
@@ -10425,7 +10434,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F257" s="7">
         <v>320</v>
@@ -10434,18 +10443,18 @@
         <v>74</v>
       </c>
       <c t="s" r="H257" s="8">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c t="s" r="I257" s="7">
         <v>182</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
       <c t="s" r="M257" s="7">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="258" ht="14.25" customHeight="1">
@@ -10460,26 +10469,28 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F258" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G258" s="8">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c t="s" r="H258" s="8">
         <v>74</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
-      <c r="M258" s="7"/>
+      <c t="s" r="M258" s="7">
+        <v>457</v>
+      </c>
     </row>
     <row r="259" ht="14.25" customHeight="1">
       <c r="A259" s="6"/>
@@ -10508,7 +10519,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -10517,18 +10528,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H260" s="8">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c t="s" r="M260" s="7">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
@@ -10543,13 +10554,13 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G261" s="8">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c t="s" r="H261" s="8">
         <v>201</v>
@@ -10558,7 +10569,7 @@
         <v>20</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -10578,7 +10589,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -10587,13 +10598,13 @@
         <v>201</v>
       </c>
       <c t="s" r="H262" s="8">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -10613,19 +10624,19 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G263" s="8">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c t="s" r="H263" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="J263" s="7">
         <v>77</v>
@@ -10633,7 +10644,7 @@
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
       <c t="s" r="M263" s="7">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="264" ht="14.25" customHeight="1">
@@ -10648,7 +10659,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -10668,7 +10679,7 @@
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
       <c t="s" r="M264" s="7">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1">
@@ -10683,7 +10694,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -10703,7 +10714,7 @@
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
       <c t="s" r="M265" s="7">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="266" ht="14.25" customHeight="1">
@@ -10733,7 +10744,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F267" s="7">
         <v>320</v>
@@ -10745,7 +10756,7 @@
         <v>74</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c t="s" r="J267" s="7">
         <v>37</v>
@@ -10753,7 +10764,7 @@
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
       <c t="s" r="M267" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="268" ht="14.25" customHeight="1">
@@ -10768,7 +10779,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F268" s="7">
         <v>320</v>
@@ -10780,15 +10791,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
       <c t="s" r="M268" s="7">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="269" ht="14.25" customHeight="1">
@@ -10803,7 +10814,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F269" s="7">
         <v>320</v>
@@ -10823,7 +10834,7 @@
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
       <c t="s" r="M269" s="7">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1">
@@ -10838,7 +10849,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F270" s="7">
         <v>320</v>
@@ -10853,12 +10864,12 @@
         <v>158</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
       <c t="s" r="M270" s="7">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="271" ht="14.25" customHeight="1">
@@ -10888,7 +10899,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -10897,20 +10908,20 @@
         <v>36</v>
       </c>
       <c t="s" r="H272" s="8">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c t="s" r="I272" s="7">
         <v>38</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="K272" s="7">
         <v>202</v>
       </c>
       <c r="L272" s="7"/>
       <c t="s" r="M272" s="7">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="273" ht="14.25" customHeight="1">
@@ -10925,19 +10936,19 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G273" s="8">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c t="s" r="H273" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c t="s" r="J273" s="7">
         <v>77</v>
@@ -10945,7 +10956,7 @@
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c t="s" r="M273" s="7">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
@@ -10960,7 +10971,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -10980,7 +10991,7 @@
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
       <c t="s" r="M274" s="7">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1">
@@ -10995,7 +11006,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -11007,15 +11018,15 @@
         <v>36</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
       <c t="s" r="M275" s="7">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="276" ht="14.25" customHeight="1">
@@ -11030,7 +11041,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -11045,12 +11056,12 @@
         <v>71</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
       <c t="s" r="M276" s="7">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="277" ht="14.25" customHeight="1">
@@ -11080,7 +11091,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F278" s="7">
         <v>320</v>
@@ -11100,7 +11111,7 @@
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
       <c t="s" r="M278" s="7">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="279" ht="14.25" customHeight="1">
@@ -11115,7 +11126,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
@@ -11127,7 +11138,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c t="s" r="J279" s="7">
         <v>112</v>
@@ -11135,7 +11146,7 @@
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -11150,7 +11161,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
@@ -11159,10 +11170,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H280" s="8">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c t="s" r="J280" s="7">
         <v>172</v>
@@ -11170,7 +11181,7 @@
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -11185,13 +11196,13 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G281" s="8">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="H281" s="8">
         <v>28</v>
@@ -11200,12 +11211,12 @@
         <v>115</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
       <c t="s" r="M281" s="7">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="282" ht="14.25" customHeight="1">
@@ -11220,7 +11231,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
@@ -11229,7 +11240,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H282" s="8">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c t="s" r="I282" s="7">
         <v>29</v>
@@ -11240,7 +11251,7 @@
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
       <c t="s" r="M282" s="7">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="283" ht="14.25" customHeight="1">
@@ -11255,13 +11266,13 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G283" s="8">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c t="s" r="H283" s="8">
         <v>28</v>
@@ -11270,12 +11281,12 @@
         <v>208</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
       <c t="s" r="M283" s="7">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="284" ht="14.25" customHeight="1">
@@ -11305,7 +11316,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
@@ -11317,7 +11328,7 @@
         <v>74</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c t="s" r="J285" s="7">
         <v>174</v>
@@ -11340,7 +11351,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -11349,7 +11360,7 @@
         <v>74</v>
       </c>
       <c t="s" r="H286" s="8">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c t="s" r="I286" s="7">
         <v>120</v>
@@ -11375,13 +11386,13 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G287" s="8">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c t="s" r="H287" s="8">
         <v>74</v>
@@ -11390,7 +11401,7 @@
         <v>62</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -11410,7 +11421,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -11419,10 +11430,10 @@
         <v>74</v>
       </c>
       <c t="s" r="H288" s="8">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c t="s" r="J288" s="7">
         <v>168</v>
@@ -11458,7 +11469,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="F290" s="7">
         <v>320</v>
@@ -11478,7 +11489,7 @@
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
       <c t="s" r="M290" s="7">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="291" ht="14.25" customHeight="1">
@@ -11493,7 +11504,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="F291" s="7">
         <v>320</v>
@@ -11505,15 +11516,15 @@
         <v>74</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
       <c t="s" r="M291" s="7">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="292" ht="14.25" customHeight="1">
@@ -11528,7 +11539,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="F292" s="7">
         <v>320</v>
@@ -11537,18 +11548,18 @@
         <v>74</v>
       </c>
       <c t="s" r="H292" s="8">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
       <c t="s" r="M292" s="7">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="293" ht="14.25" customHeight="1">
@@ -11563,27 +11574,27 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G293" s="8">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c t="s" r="H293" s="8">
         <v>74</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
       <c t="s" r="M293" s="7">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="294" ht="14.25" customHeight="1">
@@ -11613,7 +11624,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
@@ -11625,15 +11636,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
       <c t="s" r="M295" s="7">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="296" ht="14.25" customHeight="1">
@@ -11648,7 +11659,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -11660,15 +11671,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
       <c t="s" r="M296" s="7">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="297" ht="14.25" customHeight="1">
@@ -11683,7 +11694,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -11698,7 +11709,7 @@
         <v>202</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="K297" s="7">
         <v>115</v>
@@ -11720,7 +11731,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
@@ -11732,7 +11743,7 @@
         <v>74</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c t="s" r="J298" s="7">
         <v>25</v>
@@ -11742,7 +11753,7 @@
       </c>
       <c r="L298" s="7"/>
       <c t="s" r="M298" s="7">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="299" ht="14.25" customHeight="1">
@@ -11757,7 +11768,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
@@ -11769,7 +11780,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="J299" s="7">
         <v>62</v>
@@ -11777,7 +11788,7 @@
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
       <c t="s" r="M299" s="7">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="300" ht="15" customHeight="1">
@@ -11792,7 +11803,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
@@ -11807,12 +11818,12 @@
         <v>126</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
       <c t="s" r="M300" s="7">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="301" ht="14.25" customHeight="1">
@@ -11842,7 +11853,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -11854,15 +11865,15 @@
         <v>74</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
       <c t="s" r="M302" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="303" ht="14.25" customHeight="1">
@@ -11877,7 +11888,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
@@ -11889,15 +11900,15 @@
         <v>36</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
       <c t="s" r="M303" s="7">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="304" ht="14.25" customHeight="1">
@@ -11912,7 +11923,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -11924,7 +11935,7 @@
         <v>74</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c t="s" r="J304" s="7">
         <v>157</v>
@@ -11932,7 +11943,7 @@
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
       <c t="s" r="M304" s="7">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="305" ht="15" customHeight="1">
@@ -11947,7 +11958,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -11959,7 +11970,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c t="s" r="J305" s="7">
         <v>164</v>
@@ -11969,7 +11980,7 @@
       </c>
       <c r="L305" s="7"/>
       <c t="s" r="M305" s="7">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="306" ht="14.25" customHeight="1">
@@ -11984,7 +11995,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -12002,11 +12013,11 @@
         <v>86</v>
       </c>
       <c t="s" r="K306" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L306" s="7"/>
       <c t="s" r="M306" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="307" ht="14.25" customHeight="1">
@@ -12021,7 +12032,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
@@ -12033,15 +12044,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
       <c t="s" r="M307" s="7">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="308" ht="14.25" customHeight="1">
@@ -12071,7 +12082,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
@@ -12080,18 +12091,18 @@
         <v>74</v>
       </c>
       <c t="s" r="H309" s="8">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
       <c t="s" r="M309" s="7">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1">
@@ -12121,7 +12132,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -12133,7 +12144,7 @@
         <v>203</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c t="s" r="J311" s="7">
         <v>96</v>
@@ -12141,7 +12152,7 @@
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
       <c t="s" r="M311" s="7">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="312" ht="14.25" customHeight="1">
@@ -12156,7 +12167,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -12168,15 +12179,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
       <c t="s" r="M312" s="7">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="313" ht="14.25" customHeight="1">
@@ -12191,7 +12202,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -12200,18 +12211,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c t="s" r="I313" s="7">
         <v>78</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
       <c t="s" r="M313" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="314" ht="14.25" customHeight="1">
@@ -12226,19 +12237,19 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c t="s" r="H314" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c t="s" r="J314" s="7">
         <v>177</v>
@@ -12246,7 +12257,7 @@
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
       <c t="s" r="M314" s="7">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="315" ht="15" customHeight="1">
@@ -12261,7 +12272,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -12270,18 +12281,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H315" s="8">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c t="s" r="I315" s="7">
         <v>47</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c t="s" r="M315" s="7">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="316" ht="14.25" customHeight="1">
@@ -12296,13 +12307,13 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G316" s="8">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c t="s" r="H316" s="8">
         <v>28</v>
@@ -12344,7 +12355,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
@@ -12364,7 +12375,7 @@
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
       <c t="s" r="M318" s="7">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="319" ht="14.25" customHeight="1">
@@ -12379,7 +12390,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="F319" s="7">
         <v>321</v>
@@ -12391,15 +12402,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
       <c t="s" r="M319" s="7">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="320" ht="15" customHeight="1">
@@ -12414,7 +12425,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
@@ -12423,18 +12434,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c t="s" r="I320" s="7">
         <v>23</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
       <c t="s" r="M320" s="7">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="321" ht="14.25" customHeight="1">
@@ -12449,13 +12460,13 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c t="s" r="H321" s="8">
         <v>28</v>
@@ -12469,7 +12480,7 @@
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
       <c t="s" r="M321" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="322" ht="14.25" customHeight="1">
@@ -12484,7 +12495,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="F322" s="7">
         <v>321</v>
@@ -12493,7 +12504,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H322" s="8">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="I322" s="7">
         <v>124</v>
@@ -12506,7 +12517,7 @@
       </c>
       <c r="L322" s="7"/>
       <c t="s" r="M322" s="7">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="323" ht="14.25" customHeight="1">
@@ -12521,29 +12532,29 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="F323" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G323" s="8">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="H323" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c t="s" r="K323" s="7">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L323" s="7"/>
       <c t="s" r="M323" s="7">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="324" ht="14.25" customHeight="1">
@@ -12573,13 +12584,13 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G325" s="8">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c t="s" r="H325" s="8">
         <v>74</v>
@@ -12593,7 +12604,7 @@
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
       <c t="s" r="M325" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="326" ht="14.25" customHeight="1">
@@ -12608,7 +12619,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -12620,7 +12631,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c t="s" r="J326" s="7">
         <v>26</v>
@@ -12628,7 +12639,7 @@
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
       <c t="s" r="M326" s="7">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="327" ht="14.25" customHeight="1">
@@ -12643,7 +12654,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -12655,7 +12666,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J327" s="7">
         <v>145</v>
@@ -12665,7 +12676,7 @@
       </c>
       <c r="L327" s="7"/>
       <c t="s" r="M327" s="7">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="328" ht="14.25" customHeight="1">
@@ -12680,7 +12691,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
@@ -12692,7 +12703,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c t="s" r="J328" s="7">
         <v>67</v>
@@ -12702,7 +12713,7 @@
       </c>
       <c r="L328" s="7"/>
       <c t="s" r="M328" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="329" ht="14.25" customHeight="1">
@@ -12717,7 +12728,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -12729,7 +12740,7 @@
         <v>74</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c t="s" r="J329" s="7">
         <v>51</v>
@@ -12739,7 +12750,7 @@
       </c>
       <c r="L329" s="7"/>
       <c t="s" r="M329" s="7">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="330" ht="15" customHeight="1">
@@ -12769,7 +12780,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -12781,7 +12792,7 @@
         <v>74</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c t="s" r="J331" s="7">
         <v>209</v>
@@ -12789,7 +12800,7 @@
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
       <c t="s" r="M331" s="7">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="332" ht="14.25" customHeight="1">
@@ -12804,7 +12815,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
@@ -12816,7 +12827,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c t="s" r="J332" s="7">
         <v>38</v>
@@ -12824,7 +12835,7 @@
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
       <c t="s" r="M332" s="7">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="333" ht="14.25" customHeight="1">
@@ -12839,7 +12850,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -12851,15 +12862,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
       <c t="s" r="M333" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="334" ht="14.25" customHeight="1">
@@ -12874,7 +12885,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -12894,7 +12905,7 @@
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
       <c t="s" r="M334" s="7">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="335" ht="15" customHeight="1">
@@ -12909,7 +12920,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -12927,11 +12938,11 @@
         <v>62</v>
       </c>
       <c t="s" r="K335" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L335" s="7"/>
       <c t="s" r="M335" s="7">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="336" ht="14.25" customHeight="1">
@@ -12942,11 +12953,11 @@
         <v>40</v>
       </c>
       <c t="s" r="C336" s="7">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
@@ -12955,18 +12966,18 @@
         <v>74</v>
       </c>
       <c t="s" r="H336" s="8">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c t="s" r="I336" s="7">
         <v>89</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
       <c t="s" r="M336" s="7">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="337" ht="14.25" customHeight="1">
@@ -12996,7 +13007,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
@@ -13016,7 +13027,7 @@
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -13027,11 +13038,11 @@
         <v>8520</v>
       </c>
       <c t="s" r="C339" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
@@ -13040,10 +13051,10 @@
         <v>36</v>
       </c>
       <c t="s" r="H339" s="8">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c t="s" r="J339" s="7">
         <v>142</v>
@@ -13051,7 +13062,7 @@
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
       <c t="s" r="M339" s="7">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="340" ht="15" customHeight="1">
@@ -13062,17 +13073,17 @@
         <v>8521</v>
       </c>
       <c t="s" r="C340" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G340" s="8">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c t="s" r="H340" s="8">
         <v>36</v>
@@ -13086,7 +13097,7 @@
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
       <c t="s" r="M340" s="7">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="341" ht="14.25" customHeight="1">
@@ -13116,7 +13127,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="F342" s="7">
         <v>321</v>
@@ -13128,15 +13139,15 @@
         <v>74</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
       <c t="s" r="M342" s="7">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="343" ht="14.25" customHeight="1">
@@ -13151,7 +13162,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="F343" s="7">
         <v>321</v>
@@ -13163,15 +13174,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
       <c t="s" r="M343" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="344" ht="14.25" customHeight="1">
@@ -13186,7 +13197,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="F344" s="7">
         <v>321</v>
@@ -13198,15 +13209,15 @@
         <v>74</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c t="s" r="M344" s="7">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="345" ht="15" customHeight="1">
@@ -13221,7 +13232,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="F345" s="7">
         <v>321</v>
@@ -13256,7 +13267,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="F346" s="7">
         <v>321</v>
@@ -13271,14 +13282,14 @@
         <v>46</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c t="s" r="K346" s="7">
         <v>29</v>
       </c>
       <c r="L346" s="7"/>
       <c t="s" r="M346" s="7">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="347" ht="14.25" customHeight="1">
@@ -13293,7 +13304,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="F347" s="7">
         <v>321</v>
@@ -13302,18 +13313,18 @@
         <v>74</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c t="s" r="I347" s="7">
         <v>130</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
       <c t="s" r="M347" s="7">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="348" ht="14.25" customHeight="1">
@@ -13328,22 +13339,22 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="F348" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c t="s" r="H348" s="8">
         <v>74</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -13376,7 +13387,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
@@ -13391,12 +13402,12 @@
         <v>76</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
       <c t="s" r="M350" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="351" ht="14.25" customHeight="1">
@@ -13411,7 +13422,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -13423,7 +13434,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c t="s" r="J351" s="7">
         <v>176</v>
@@ -13431,7 +13442,7 @@
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
       <c t="s" r="M351" s="7">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
@@ -13446,7 +13457,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
@@ -13458,15 +13469,15 @@
         <v>36</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
       <c t="s" r="M352" s="7">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="353" ht="14.25" customHeight="1">
@@ -13481,7 +13492,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -13493,15 +13504,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
       <c t="s" r="M353" s="7">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="354" ht="14.25" customHeight="1">
@@ -13516,7 +13527,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
@@ -13525,7 +13536,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c t="s" r="I354" s="7">
         <v>67</v>
@@ -13536,7 +13547,7 @@
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
       <c t="s" r="M354" s="7">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="355" ht="15" customHeight="1">
@@ -13551,22 +13562,22 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c t="s" r="H355" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -13599,7 +13610,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -13608,7 +13619,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H357" s="8">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c t="s" r="I357" s="7">
         <v>168</v>
@@ -13619,7 +13630,7 @@
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
       <c t="s" r="M357" s="7">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="358" ht="14.25" customHeight="1">
@@ -13634,13 +13645,13 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G358" s="8">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c t="s" r="H358" s="8">
         <v>28</v>
@@ -13654,7 +13665,7 @@
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
       <c t="s" r="M358" s="7">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="359" ht="14.25" customHeight="1">
@@ -13669,7 +13680,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -13689,7 +13700,7 @@
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
       <c t="s" r="M359" s="7">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="360" ht="15" customHeight="1">
@@ -13704,7 +13715,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -13716,10 +13727,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -13754,7 +13765,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -13774,7 +13785,7 @@
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
       <c t="s" r="M362" s="7">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="363" ht="14.25" customHeight="1">
@@ -13789,7 +13800,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -13801,10 +13812,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -13824,7 +13835,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -13836,15 +13847,15 @@
         <v>74</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
       <c t="s" r="M364" s="7">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="365" ht="15" customHeight="1">
@@ -13859,7 +13870,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -13871,15 +13882,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
       <c t="s" r="M365" s="7">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="366" ht="14.25" customHeight="1">
@@ -13894,7 +13905,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
@@ -13909,12 +13920,12 @@
         <v>51</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
       <c t="s" r="M366" s="7">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="367" ht="14.25" customHeight="1">
@@ -13944,7 +13955,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
@@ -13953,7 +13964,7 @@
         <v>74</v>
       </c>
       <c t="s" r="H368" s="8">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c t="s" r="I368" s="7">
         <v>79</v>
@@ -13966,7 +13977,7 @@
       </c>
       <c r="L368" s="7"/>
       <c t="s" r="M368" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="369" ht="14.25" customHeight="1">
@@ -13981,13 +13992,13 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G369" s="8">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c t="s" r="H369" s="8">
         <v>74</v>
@@ -13996,14 +14007,14 @@
         <v>144</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c t="s" r="K369" s="7">
         <v>144</v>
       </c>
       <c r="L369" s="7"/>
       <c t="s" r="M369" s="7">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="370" ht="15" customHeight="1">
@@ -14018,7 +14029,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="F370" s="7">
         <v>320</v>
@@ -14027,13 +14038,13 @@
         <v>74</v>
       </c>
       <c t="s" r="H370" s="8">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -14053,27 +14064,27 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G371" s="8">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c t="s" r="H371" s="8">
         <v>74</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>571</v>
+        <v>248</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
       <c t="s" r="M371" s="7">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="372" ht="14.25" customHeight="1">
@@ -14103,7 +14114,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
@@ -14115,7 +14126,7 @@
         <v>139</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c t="s" r="J373" s="7">
         <v>204</v>
@@ -14123,7 +14134,7 @@
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
       <c t="s" r="M373" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="374" ht="14.25" customHeight="1">
@@ -14138,7 +14149,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -14150,15 +14161,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
       <c t="s" r="M374" s="7">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="375" ht="15" customHeight="1">
@@ -14173,7 +14184,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
@@ -14182,18 +14193,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H375" s="8">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c t="s" r="I375" s="7">
         <v>102</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
       <c t="s" r="M375" s="7">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="376" ht="14.25" customHeight="1">
@@ -14208,22 +14219,22 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G376" s="8">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c t="s" r="H376" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -14256,7 +14267,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -14276,7 +14287,7 @@
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
       <c t="s" r="M378" s="7">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="379" ht="14.25" customHeight="1">
@@ -14291,7 +14302,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -14300,7 +14311,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H379" s="8">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="I379" s="7">
         <v>175</v>
@@ -14311,7 +14322,7 @@
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
       <c t="s" r="M379" s="7">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="380" ht="15" customHeight="1">
@@ -14326,13 +14337,13 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G380" s="8">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="H380" s="8">
         <v>28</v>
@@ -14346,7 +14357,7 @@
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
       <c t="s" r="M380" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="381" ht="14.25" customHeight="1">
@@ -14361,7 +14372,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -14373,7 +14384,7 @@
         <v>74</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c t="s" r="J381" s="7">
         <v>192</v>
@@ -14381,7 +14392,7 @@
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c t="s" r="M381" s="7">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
@@ -14411,7 +14422,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -14423,17 +14434,17 @@
         <v>139</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c t="s" r="K383" s="7">
         <v>149</v>
       </c>
       <c r="L383" s="7"/>
       <c t="s" r="M383" s="7">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="384" ht="14.25" customHeight="1">
@@ -14448,7 +14459,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -14460,17 +14471,17 @@
         <v>28</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c t="s" r="K384" s="7">
         <v>96</v>
       </c>
       <c r="L384" s="7"/>
       <c t="s" r="M384" s="7">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="385" ht="15" customHeight="1">
@@ -14485,7 +14496,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -14505,7 +14516,7 @@
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
       <c t="s" r="M385" s="7">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="386" ht="14.25" customHeight="1">
@@ -14520,7 +14531,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
@@ -14535,12 +14546,12 @@
         <v>42</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
       <c t="s" r="M386" s="7">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="387" ht="14.25" customHeight="1">
@@ -14555,7 +14566,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -14567,17 +14578,17 @@
         <v>108</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c t="s" r="K387" s="7">
         <v>61</v>
       </c>
       <c r="L387" s="7"/>
       <c t="s" r="M387" s="7">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="388" ht="14.25" customHeight="1">
@@ -14592,7 +14603,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
@@ -14607,14 +14618,14 @@
         <v>125</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c t="s" r="K388" s="7">
         <v>180</v>
       </c>
       <c r="L388" s="7"/>
       <c t="s" r="M388" s="7">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="389" ht="14.25" customHeight="1">
@@ -14644,7 +14655,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
@@ -14659,12 +14670,12 @@
         <v>135</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c t="s" r="M390" s="7">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
@@ -14679,7 +14690,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
@@ -14691,15 +14702,15 @@
         <v>74</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
       <c t="s" r="M391" s="7">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="392" ht="14.25" customHeight="1">
@@ -14714,7 +14725,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
@@ -14726,17 +14737,17 @@
         <v>28</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c t="s" r="K392" s="7">
         <v>54</v>
       </c>
       <c r="L392" s="7"/>
       <c t="s" r="M392" s="7">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="393" ht="14.25" customHeight="1">
@@ -14751,7 +14762,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
@@ -14760,18 +14771,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H393" s="8">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c t="s" r="I393" s="7">
         <v>120</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
       <c t="s" r="M393" s="7">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="394" ht="14.25" customHeight="1">
@@ -14786,27 +14797,27 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F394" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G394" s="8">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c t="s" r="H394" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
       <c t="s" r="M394" s="7">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="395" ht="15" customHeight="1">
@@ -14821,7 +14832,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F395" s="7">
         <v>320</v>
@@ -14830,7 +14841,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H395" s="8">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c t="s" r="I395" s="7">
         <v>125</v>
@@ -14841,7 +14852,7 @@
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
       <c t="s" r="M395" s="7">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="396" ht="14.25" customHeight="1">
@@ -14856,13 +14867,13 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="F396" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G396" s="8">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c t="s" r="H396" s="8">
         <v>28</v>
@@ -14871,12 +14882,12 @@
         <v>165</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
       <c t="s" r="M396" s="7">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="397" ht="14.25" customHeight="1">
@@ -14902,11 +14913,11 @@
         <v>664</v>
       </c>
       <c t="s" r="C398" s="7">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="F398" s="7">
         <v>330</v>
@@ -14921,12 +14932,12 @@
         <v>137</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
       <c t="s" r="M398" s="7">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="399" ht="14.25" customHeight="1">
@@ -14941,7 +14952,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="F399" s="7">
         <v>330</v>
@@ -14950,7 +14961,7 @@
         <v>57</v>
       </c>
       <c t="s" r="H399" s="8">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c t="s" r="I399" s="7">
         <v>174</v>
@@ -14961,7 +14972,7 @@
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
       <c t="s" r="M399" s="7">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="400" ht="15" customHeight="1">
@@ -14976,13 +14987,13 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="F400" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G400" s="8">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c t="s" r="H400" s="8">
         <v>57</v>
@@ -14991,12 +15002,12 @@
         <v>160</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
       <c t="s" r="M400" s="7">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="401" ht="14.25" customHeight="1">
@@ -15026,19 +15037,19 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="F402" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G402" s="8">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c t="s" r="H402" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c t="s" r="J402" s="7">
         <v>177</v>
@@ -15048,7 +15059,7 @@
       </c>
       <c r="L402" s="7"/>
       <c t="s" r="M402" s="7">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="403" ht="14.25" customHeight="1">
@@ -15063,7 +15074,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="F403" s="7">
         <v>330</v>
@@ -15072,10 +15083,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H403" s="8">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="J403" s="7">
         <v>69</v>
@@ -15100,25 +15111,25 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="F404" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G404" s="8">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c t="s" r="H404" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c t="s" r="K404" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="L404" s="7"/>
       <c t="s" r="M404" s="7">
@@ -15152,7 +15163,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F406" s="7">
         <v>330</v>
@@ -15172,7 +15183,7 @@
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -15187,7 +15198,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F407" s="7">
         <v>330</v>
@@ -15202,12 +15213,12 @@
         <v>137</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
       <c t="s" r="M407" s="7">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="408" ht="14.25" customHeight="1">
@@ -15222,7 +15233,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F408" s="7">
         <v>330</v>
@@ -15231,13 +15242,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H408" s="8">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -15257,27 +15268,27 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="F409" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c t="s" r="H409" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
       <c t="s" r="M409" s="7">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="410" ht="15" customHeight="1">
@@ -15307,7 +15318,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F411" s="7">
         <v>330</v>
@@ -15327,7 +15338,7 @@
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
       <c t="s" r="M411" s="7">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="412" ht="14.25" customHeight="1">
@@ -15342,7 +15353,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F412" s="7">
         <v>330</v>
@@ -15354,15 +15365,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
       <c t="s" r="M412" s="7">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="413" ht="14.25" customHeight="1">
@@ -15377,7 +15388,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="F413" s="7">
         <v>330</v>
@@ -15386,10 +15397,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H413" s="8">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c t="s" r="J413" s="7">
         <v>112</v>
@@ -15399,7 +15410,7 @@
       </c>
       <c r="L413" s="7"/>
       <c t="s" r="M413" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="414" ht="14.25" customHeight="1">
@@ -15429,7 +15440,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="F415" s="7">
         <v>330</v>
@@ -15438,7 +15449,7 @@
         <v>57</v>
       </c>
       <c t="s" r="H415" s="8">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c t="s" r="I415" s="7">
         <v>93</v>
@@ -15449,7 +15460,7 @@
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
       <c t="s" r="M415" s="7">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="416" ht="14.25" customHeight="1">
@@ -15464,29 +15475,29 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="F416" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G416" s="8">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c t="s" r="H416" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c t="s" r="K416" s="7">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="L416" s="7"/>
       <c t="s" r="M416" s="7">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="417" ht="14.25" customHeight="1">
@@ -15516,7 +15527,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="F418" s="7">
         <v>330</v>
@@ -15525,16 +15536,16 @@
         <v>28</v>
       </c>
       <c t="s" r="H418" s="8">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c t="s" r="I418" s="7">
         <v>172</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c t="s" r="K418" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L418" s="7"/>
       <c t="s" r="M418" s="7">
@@ -15553,34 +15564,34 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="F419" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G419" s="8">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c t="s" r="H419" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c t="s" r="K419" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="L419" s="7"/>
       <c t="s" r="M419" s="7">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="420" ht="16.5" customHeight="1">
       <c t="s" r="A420" s="9">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B420" s="9"/>
       <c r="C420" s="9"/>
@@ -15600,7 +15611,7 @@
     <row r="421" ht="65.25" customHeight="1"/>
     <row r="422" ht="16.5" customHeight="1">
       <c t="s" r="A422" s="10">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B422" s="10"/>
       <c r="C422" s="10"/>
@@ -15613,7 +15624,7 @@
       <c r="J422" s="10"/>
       <c r="K422" s="10"/>
       <c t="s" r="L422" s="11">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="M422" s="11"/>
       <c r="N422" s="11"/>
